--- a/ICME_density_pileup_search_PSP_SOLO/结果_SOLO_多参数密度堆积区/SOLO_ICME_密度堆积区结果.xlsx
+++ b/ICME_density_pileup_search_PSP_SOLO/结果_SOLO_多参数密度堆积区/SOLO_ICME_密度堆积区结果.xlsx
@@ -873,7 +873,7 @@
         <v>44327.48541666667</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>44326.26666666667</v>
+        <v>44326.27361111111</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>44326.76388888889</v>
@@ -931,16 +931,16 @@
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.212021018740831</v>
+        <v>8.212021018740829</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.544538974345652</v>
+        <v>9.544538974345661</v>
       </c>
       <c r="AC3" t="n">
         <v>5.829743344244465</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8603894898238209</v>
+        <v>0.86038948982382</v>
       </c>
       <c r="AE3" t="n">
         <v>1.408641947650803</v>
@@ -1511,7 +1511,7 @@
         <v>44431.14513888889</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44430.32569444444</v>
+        <v>44430.33055555556</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>44430.68333333333</v>
@@ -1831,7 +1831,7 @@
         <v>44437.05208333334</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>44436.55763888889</v>
+        <v>44436.56111111111</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>44436.77777777778</v>
@@ -1889,16 +1889,16 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>43.97794504186979</v>
+        <v>43.97794504186977</v>
       </c>
       <c r="AB9" t="n">
-        <v>49.11587562561036</v>
+        <v>49.11587562561035</v>
       </c>
       <c r="AC9" t="n">
         <v>40.25005461692805</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.8953916525299305</v>
+        <v>0.8953916525299302</v>
       </c>
       <c r="AE9" t="n">
         <v>1.092618269973077</v>
@@ -1907,13 +1907,13 @@
         <v>0.2470101070058711</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4421466338697678</v>
+        <v>0.4421466338697675</v>
       </c>
       <c r="AH9" t="n">
         <v>0.1311776473280266</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.5586610596669765</v>
+        <v>0.5586610596669768</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.883019798244975</v>
@@ -1992,7 +1992,7 @@
         <v>44437.79722222222</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>44437.08055555556</v>
+        <v>44437.08194444444</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>44437.27569444444</v>
@@ -2056,7 +2056,7 @@
         <v>144.8466744719611</v>
       </c>
       <c r="AC10" t="n">
-        <v>147.3419788996379</v>
+        <v>147.3419788996378</v>
       </c>
       <c r="AD10" t="n">
         <v>1.665574433552811</v>
@@ -2065,7 +2065,7 @@
         <v>1.637367161669348</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.095185407793283</v>
+        <v>1.095185407793284</v>
       </c>
       <c r="AG10" t="n">
         <v>0.5469295691226392</v>
@@ -2074,10 +2074,10 @@
         <v>0.3972450025541046</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.002424936633307</v>
+        <v>2.002424936633309</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.756952008840235</v>
+        <v>2.756952008840237</v>
       </c>
       <c r="AK10" t="n">
         <v>15.6104772567749</v>
@@ -2153,7 +2153,7 @@
         <v>44465.99930555555</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>44464.76805555556</v>
+        <v>44464.77708333333</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>44465.35486111111</v>
@@ -2217,13 +2217,13 @@
         <v>73.44536279890281</v>
       </c>
       <c r="AC11" t="n">
-        <v>56.23387045179087</v>
+        <v>56.2338704517909</v>
       </c>
       <c r="AD11" t="n">
         <v>0.6740889399017306</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.8804072412595904</v>
+        <v>0.8804072412595899</v>
       </c>
       <c r="AF11" t="n">
         <v>1.361933538522787</v>
@@ -2235,7 +2235,7 @@
         <v>2.605202280927377</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.7047781526800565</v>
+        <v>0.7047781526800564</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.5227745839520676</v>
@@ -2314,7 +2314,7 @@
         <v>44474.45833333334</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>44474.07638888889</v>
+        <v>44474.07916666667</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>44474.26319444444</v>
@@ -2390,13 +2390,13 @@
         <v>0.6829493298799998</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.7521813080006834</v>
+        <v>0.7521813080006836</v>
       </c>
       <c r="AH12" t="n">
         <v>0.4765269835462254</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.9079583906376191</v>
+        <v>0.9079583906376189</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.43318081338777</v>
@@ -2475,7 +2475,7 @@
         <v>44484.96597222222</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>44483.96666666667</v>
+        <v>44483.97569444445</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>44484.52291666667</v>
@@ -2536,13 +2536,13 @@
         <v>29.86954383757668</v>
       </c>
       <c r="AB13" t="n">
-        <v>23.86240883077894</v>
+        <v>23.86240883077895</v>
       </c>
       <c r="AC13" t="n">
         <v>24.11373533725752</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.251740511588647</v>
+        <v>1.251740511588646</v>
       </c>
       <c r="AE13" t="n">
         <v>1.238694189009614</v>
@@ -2557,10 +2557,10 @@
         <v>0.2210650362068937</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.001613726295742</v>
+        <v>2.001613726295743</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.884476078004691</v>
+        <v>5.884476078004692</v>
       </c>
       <c r="AK13" t="n">
         <v>6.589552554033217</v>
@@ -2636,7 +2636,7 @@
         <v>44500.325</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>44499.91736111111</v>
+        <v>44499.92152777778</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>44500.14166666667</v>
@@ -2797,7 +2797,7 @@
         <v>44504.82430555556</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>44503.58541666667</v>
+        <v>44503.59513888889</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>44504.21180555555</v>
@@ -2820,13 +2820,13 @@
         <v>1</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>44503.58819444444</v>
+        <v>44503.59513888889</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>44504.21180555555</v>
+        <v>44504.10972222222</v>
       </c>
       <c r="R15" t="n">
-        <v>898</v>
+        <v>741</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2855,61 +2855,61 @@
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.54096012193357</v>
+        <v>20.15083859366872</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.774211997922162</v>
+        <v>10.40394265784158</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.06816516664303</v>
+        <v>21.59284485710985</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.341060385456599</v>
+        <v>1.936846372224168</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.077238420289488</v>
+        <v>0.9332183288962815</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.6969271221572251</v>
+        <v>0.77300188536128</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.3473305948903704</v>
+        <v>0.3863930163986595</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.3155585930497703</v>
+        <v>0.2946032134209844</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.006523849064317</v>
+        <v>2.000558634744419</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.20855060678796</v>
+        <v>2.623874588416895</v>
       </c>
       <c r="AK15" t="n">
-        <v>14.52187956530883</v>
+        <v>14.30118587363496</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.452488187948862</v>
+        <v>9.456507838765781</v>
       </c>
       <c r="AM15" t="n">
-        <v>11.32627151012421</v>
+        <v>15.90383024215698</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.718059728969915</v>
+        <v>1.512311533757634</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.282141219405536</v>
+        <v>0.8992290319929459</v>
       </c>
       <c r="AP15" t="n">
         <v>100</v>
       </c>
       <c r="AQ15" s="2" t="n">
-        <v>44503.59166666667</v>
+        <v>44503.59513888889</v>
       </c>
       <c r="AR15" s="2" t="n">
-        <v>44503.7375</v>
+        <v>44503.73680555556</v>
       </c>
       <c r="AS15" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44529.28472222222</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44527.95833333334</v>
+        <v>44527.96875</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>44528.63888888889</v>
@@ -2981,13 +2981,13 @@
         <v>1</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>44527.95833333334</v>
+        <v>44527.96875</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>44528.63888888889</v>
       </c>
       <c r="R16" t="n">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3016,61 +3016,61 @@
         <v>2</v>
       </c>
       <c r="AA16" t="n">
-        <v>23.38427063680525</v>
+        <v>23.29900832452561</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.78789624770482</v>
+        <v>11.48525921238793</v>
       </c>
       <c r="AC16" t="n">
         <v>10.84536388715111</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.660963440813567</v>
+        <v>2.028601000088482</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.156153622886681</v>
+        <v>2.148291986046569</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.6076798477489121</v>
+        <v>0.6107608989331826</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1789431948415652</v>
+        <v>0.2090870249095599</v>
       </c>
       <c r="AH16" t="n">
         <v>0.1201335826989435</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.395937175967751</v>
+        <v>2.921084649788125</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5.058367811037205</v>
+        <v>5.084014687747706</v>
       </c>
       <c r="AK16" t="n">
-        <v>7.075159577945513</v>
+        <v>7.01431559825731</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.745255969961484</v>
+        <v>3.717055204510689</v>
       </c>
       <c r="AM16" t="n">
         <v>9.061122481028239</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.577231287487111</v>
+        <v>1.887062529968712</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.7808259509524517</v>
+        <v>0.7741111118344953</v>
       </c>
       <c r="AP16" t="n">
-        <v>99.28571428571429</v>
+        <v>99.27461139896373</v>
       </c>
       <c r="AQ16" s="2" t="n">
-        <v>44527.95833333334</v>
+        <v>44527.96875</v>
       </c>
       <c r="AR16" s="2" t="n">
         <v>44528.63888888889</v>
       </c>
       <c r="AS16" t="n">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>44557.77361111111</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44557.42847222222</v>
+        <v>44557.43125</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>44557.59583333333</v>
@@ -3189,22 +3189,22 @@
         <v>1.7466904190989</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.9769137163416711</v>
+        <v>0.9769137163416709</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.56063703229911</v>
+        <v>1.560637032299109</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.5901554796724316</v>
+        <v>0.5901554796724315</v>
       </c>
       <c r="AH17" t="n">
         <v>0.7772997739405815</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.644450633865754</v>
+        <v>2.644450633865753</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.007767253536354</v>
+        <v>2.007767253536353</v>
       </c>
       <c r="AK17" t="n">
         <v>5.610852321229315</v>
@@ -3439,7 +3439,7 @@
         <v>44588.30208333334</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>44586.54513888889</v>
+        <v>44586.54652777778</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>44586.92777777778</v>
@@ -3462,13 +3462,13 @@
         <v>1</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>44586.54513888889</v>
+        <v>44586.54652777778</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>44586.67916666667</v>
       </c>
       <c r="R19" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3497,61 +3497,61 @@
         <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.718819346082029</v>
+        <v>7.666696896602974</v>
       </c>
       <c r="AB19" t="n">
-        <v>14.53178544860137</v>
+        <v>14.61938948359406</v>
       </c>
       <c r="AC19" t="n">
         <v>2.471502326329528</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.5311679953838663</v>
+        <v>0.5244197717836695</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.123128497129673</v>
+        <v>3.102039118040776</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.3281870338257742</v>
+        <v>0.3246640000522936</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.274438730761438</v>
+        <v>2.259198249464377</v>
       </c>
       <c r="AH19" t="n">
         <v>0.07076318797967503</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.1442936357823557</v>
+        <v>0.1437076184567984</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.6378214887667</v>
+        <v>4.588035238682934</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.189920596189681</v>
+        <v>2.19127175101708</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.669490937764446</v>
+        <v>3.653930358464519</v>
       </c>
       <c r="AM19" t="n">
         <v>8.165798167387644</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.5967913896862873</v>
+        <v>0.5997026587933965</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.2681820627083008</v>
+        <v>0.2683475278348815</v>
       </c>
       <c r="AP19" t="n">
         <v>95</v>
       </c>
       <c r="AQ19" s="2" t="n">
-        <v>44586.54513888889</v>
+        <v>44586.54652777778</v>
       </c>
       <c r="AR19" s="2" t="n">
         <v>44586.67916666667</v>
       </c>
       <c r="AS19" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44628.61388888889</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44627.93472222222</v>
+        <v>44627.94097222222</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>44628.31736111111</v>
@@ -3761,7 +3761,7 @@
         <v>44629.28888888889</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>44628.61527777778</v>
+        <v>44628.62152777778</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>44628.97777777778</v>
@@ -3784,13 +3784,13 @@
         <v>1</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>44628.61527777778</v>
+        <v>44628.62152777778</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>44628.97777777778</v>
       </c>
       <c r="R21" t="n">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -3819,61 +3819,61 @@
         <v>2</v>
       </c>
       <c r="AA21" t="n">
-        <v>85.27499118715733</v>
+        <v>85.41103294073584</v>
       </c>
       <c r="AB21" t="n">
-        <v>37.96732224676344</v>
+        <v>40.54900865024992</v>
       </c>
       <c r="AC21" t="n">
         <v>27.38621764200725</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.246010151385556</v>
+        <v>2.106365501495668</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.113792211172509</v>
+        <v>3.118759737369695</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.4992768453218858</v>
+        <v>0.5052213231951264</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1011560615462179</v>
+        <v>0.105946663867639</v>
       </c>
       <c r="AH21" t="n">
         <v>0.2166441343635967</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.935708623785911</v>
+        <v>4.768638338875002</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.304594337569015</v>
+        <v>2.332033242807335</v>
       </c>
       <c r="AK21" t="n">
-        <v>23.35546403563799</v>
+        <v>23.49223431474284</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.465805251019386</v>
+        <v>4.950986558812049</v>
       </c>
       <c r="AM21" t="n">
         <v>2.131378297100309</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.229843829465416</v>
+        <v>4.744960228770974</v>
       </c>
       <c r="AO21" t="n">
-        <v>10.95791585539393</v>
+        <v>11.0220857304888</v>
       </c>
       <c r="AP21" t="n">
         <v>100</v>
       </c>
       <c r="AQ21" s="2" t="n">
-        <v>44628.61527777778</v>
+        <v>44628.62152777778</v>
       </c>
       <c r="AR21" s="2" t="n">
         <v>44628.97777777778</v>
       </c>
       <c r="AS21" t="n">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44632.29097222222</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44631.82847222222</v>
+        <v>44631.83125</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>44632.01875</v>
@@ -3945,13 +3945,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>44631.82847222222</v>
+        <v>44631.83125</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>44631.91875</v>
       </c>
       <c r="R22" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S22" t="n">
         <v>47</v>
@@ -3980,61 +3980,61 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>150.9728248204941</v>
+        <v>151.7087692624048</v>
       </c>
       <c r="AB22" t="n">
-        <v>49.66931455256444</v>
+        <v>52.6785768462741</v>
       </c>
       <c r="AC22" t="n">
         <v>101.0565966544331</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.039559256665831</v>
+        <v>2.879894984732013</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.493943293348296</v>
+        <v>1.501225791139382</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.161206342904629</v>
+        <v>1.169697298598723</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.1326560840380615</v>
+        <v>0.1567647009996635</v>
       </c>
       <c r="AH22" t="n">
         <v>0.3317130451362416</v>
       </c>
       <c r="AI22" t="n">
-        <v>8.753509884789436</v>
+        <v>7.461483938282979</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.500635142123209</v>
+        <v>3.526232434176061</v>
       </c>
       <c r="AK22" t="n">
-        <v>34.91961621733812</v>
+        <v>35.22085730471309</v>
       </c>
       <c r="AL22" t="n">
-        <v>25.49669873366753</v>
+        <v>25.78300607427955</v>
       </c>
       <c r="AM22" t="n">
         <v>52.46676479578018</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.369574021409601</v>
+        <v>1.366049296317255</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.6655568787833218</v>
+        <v>0.6712984389604645</v>
       </c>
       <c r="AP22" t="n">
         <v>90</v>
       </c>
       <c r="AQ22" s="2" t="n">
-        <v>44631.82847222222</v>
+        <v>44631.83125</v>
       </c>
       <c r="AR22" s="2" t="n">
         <v>44631.91875</v>
       </c>
       <c r="AS22" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>44660.99930555555</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>44659.57638888889</v>
+        <v>44659.58194444444</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>44660.075</v>
@@ -4099,20 +4099,20 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>最近候选簇内有 7 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>44659.57638888889</v>
+        <v>44659.84236111111</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>44659.875</v>
+        <v>44659.84583333333</v>
       </c>
       <c r="R23" t="n">
-        <v>430</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4121,95 +4121,95 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="W23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="b">
         <v>0</v>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>150.8116165770302</v>
+        <v>222.5256577555352</v>
       </c>
       <c r="AB23" t="n">
-        <v>75.33469656915493</v>
+        <v>177.8644272698296</v>
       </c>
       <c r="AC23" t="n">
-        <v>67.66602703730253</v>
+        <v>99.9234495247736</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.001887887589615</v>
+        <v>1.251097035934859</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.228764169852793</v>
+        <v>2.226961327034305</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.4719383824369683</v>
+        <v>0.5487960523877973</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.2795272585447354</v>
+        <v>0.4151669693601446</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.05877101606660299</v>
+        <v>0.102766471286949</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.688344760700465</v>
+        <v>1.321868291289169</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8.030121206380679</v>
+        <v>5.340224739793052</v>
       </c>
       <c r="AK23" t="n">
-        <v>21.51224285008949</v>
+        <v>11.25198662281036</v>
       </c>
       <c r="AL23" t="n">
-        <v>6.892309702342997</v>
+        <v>20.83253039469322</v>
       </c>
       <c r="AM23" t="n">
-        <v>32.74535516103109</v>
+        <v>33.1278157711029</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.121195038983309</v>
+        <v>0.5401161745419387</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.6569555512315938</v>
+        <v>0.3396537429619906</v>
       </c>
       <c r="AP23" t="n">
-        <v>94.16666666666667</v>
+        <v>100</v>
       </c>
       <c r="AQ23" s="2" t="n">
-        <v>44659.57638888889</v>
+        <v>44659.84236111111</v>
       </c>
       <c r="AR23" s="2" t="n">
-        <v>44659.875</v>
+        <v>44659.84583333333</v>
       </c>
       <c r="AS23" t="n">
-        <v>430</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="AU23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="b">
         <v>0</v>
       </c>
       <c r="AW23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4244,7 +4244,7 @@
         <v>44698.41666666666</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>44697.07986111111</v>
+        <v>44697.08333333334</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>44697.48333333333</v>
@@ -4405,7 +4405,7 @@
         <v>44703.08402777778</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>44702.61875</v>
+        <v>44702.62083333333</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>44702.76944444444</v>
@@ -4421,7 +4421,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>最近候选簇内有 3 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -4466,31 +4466,31 @@
         <v>53.73324219484286</v>
       </c>
       <c r="AB25" t="n">
-        <v>39.04086153162131</v>
+        <v>39.04086153162132</v>
       </c>
       <c r="AC25" t="n">
-        <v>44.43718642540793</v>
+        <v>44.43718642540792</v>
       </c>
       <c r="AD25" t="n">
         <v>1.376333412912043</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.209195417559553</v>
+        <v>1.209195417559554</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.492125970712757</v>
+        <v>1.492125970712771</v>
       </c>
       <c r="AG25" t="n">
         <v>0.7416759882315224</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.4624264080994133</v>
+        <v>0.4624264080994124</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.011829955922711</v>
+        <v>2.01182995592273</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.226731744939569</v>
+        <v>3.226731744939604</v>
       </c>
       <c r="AK25" t="n">
         <v>7.498765659332276</v>
@@ -4566,7 +4566,7 @@
         <v>44721.25</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>44721.01944444444</v>
+        <v>44721.02013888889</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>44721.08333333334</v>
@@ -4627,7 +4627,7 @@
         <v>2.728074436717539</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.927426074081</v>
+        <v>9.927426074080996</v>
       </c>
       <c r="AC26" t="n">
         <v>1.39739618930551</v>
@@ -4642,7 +4642,7 @@
         <v>0.08267824865039113</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.361951252849645</v>
+        <v>3.361951252849646</v>
       </c>
       <c r="AH26" t="n">
         <v>0.02981281590291331</v>
@@ -4727,7 +4727,7 @@
         <v>44730.43125</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>44729.02916666667</v>
+        <v>44729.04236111111</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>44729.82361111111</v>
@@ -4743,20 +4743,20 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>检测到 2 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。</t>
         </is>
       </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>44729.02916666667</v>
+        <v>44729.44027777778</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>44729.82361111111</v>
+        <v>44729.78055555555</v>
       </c>
       <c r="R27" t="n">
-        <v>1144</v>
+        <v>490</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -4765,18 +4765,18 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="W27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="b">
         <v>0</v>
@@ -4785,72 +4785,72 @@
         <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>27.07796481215239</v>
+        <v>22.78634056826096</v>
       </c>
       <c r="AB27" t="n">
-        <v>12.51836728828122</v>
+        <v>26.57975114822381</v>
       </c>
       <c r="AC27" t="n">
-        <v>6.49425295193984</v>
+        <v>7.737453676064858</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.163058822974527</v>
+        <v>0.8572819377123345</v>
       </c>
       <c r="AE27" t="n">
-        <v>4.169527274736684</v>
+        <v>2.944940483294721</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.493089876463103</v>
+        <v>0.4192674777284673</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.993452254243599</v>
+        <v>0.2095581523895248</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.1168497800545159</v>
+        <v>0.1678850488200264</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.4987852651888663</v>
+        <v>2.000721389016337</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12.77785782537637</v>
+        <v>2.497348517186448</v>
       </c>
       <c r="AK27" t="n">
-        <v>7.187261103060572</v>
+        <v>6.113323883619159</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.20581245093296</v>
+        <v>12.85361258188883</v>
       </c>
       <c r="AM27" t="n">
-        <v>5.276926083366076</v>
+        <v>2.796825299365446</v>
       </c>
       <c r="AN27" t="n">
-        <v>3.258328286260549</v>
+        <v>0.475611338421156</v>
       </c>
       <c r="AO27" t="n">
-        <v>1.362016634213667</v>
+        <v>2.185808275191937</v>
       </c>
       <c r="AP27" t="n">
-        <v>99.47552447552448</v>
+        <v>98.77551020408163</v>
       </c>
       <c r="AQ27" s="2" t="n">
-        <v>44729.02916666667</v>
+        <v>44729.44027777778</v>
       </c>
       <c r="AR27" s="2" t="n">
-        <v>44729.82361111111</v>
+        <v>44729.78055555555</v>
       </c>
       <c r="AS27" t="n">
-        <v>1144</v>
+        <v>490</v>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="AU27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW27" t="b">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>44740.81875</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>44740.34027777778</v>
+        <v>44740.34375</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>44740.57013888889</v>
@@ -5108,7 +5108,7 @@
         <v>30.21635105055994</v>
       </c>
       <c r="AB29" t="n">
-        <v>17.72043856352526</v>
+        <v>17.72043856352525</v>
       </c>
       <c r="AC29" t="n">
         <v>32.02200518925981</v>
@@ -5123,13 +5123,13 @@
         <v>0.5344762476114459</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.183571326101712</v>
+        <v>1.183571326101711</v>
       </c>
       <c r="AH29" t="n">
         <v>0.7421126681249632</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.4515792464927585</v>
+        <v>0.4515792464927587</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.7202090337062488</v>
@@ -5208,7 +5208,7 @@
         <v>44745.92986111111</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>44745.25069444445</v>
+        <v>44745.25833333333</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>44745.67152777778</v>
@@ -5231,19 +5231,19 @@
         <v>1</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>44745.25069444445</v>
+        <v>44745.25833333333</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>44745.57638888889</v>
+        <v>44745.57777777778</v>
       </c>
       <c r="R30" t="n">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="S30" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T30" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -5266,61 +5266,61 @@
         <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>13.06666572478139</v>
+        <v>13.05564168177312</v>
       </c>
       <c r="AB30" t="n">
-        <v>5.813536228868699</v>
+        <v>6.532478172249267</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.99731738090515</v>
+        <v>13.00107596503363</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.247627813841652</v>
+        <v>1.998574099678591</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.005335589017633</v>
+        <v>1.004197015453663</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.648469209045497</v>
+        <v>1.665427947786369</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.7247440893039827</v>
+        <v>0.7158273532574928</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.8199637757637827</v>
+        <v>0.8318979462693666</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.274553505677605</v>
+        <v>2.326577686934648</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.010417115695112</v>
+        <v>2.001961845506357</v>
       </c>
       <c r="AK30" t="n">
-        <v>4.488490314896046</v>
+        <v>4.509161480111272</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.417741578072309</v>
+        <v>2.567114408810933</v>
       </c>
       <c r="AM30" t="n">
-        <v>8.04880344470342</v>
+        <v>8.041838697592418</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.856480591476102</v>
+        <v>1.756509746754871</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.5576593273438343</v>
+        <v>0.5607127486231768</v>
       </c>
       <c r="AP30" t="n">
-        <v>98.50746268656717</v>
+        <v>98.47826086956522</v>
       </c>
       <c r="AQ30" s="2" t="n">
-        <v>44745.25069444445</v>
+        <v>44745.25833333333</v>
       </c>
       <c r="AR30" s="2" t="n">
-        <v>44745.57638888889</v>
+        <v>44745.57777777778</v>
       </c>
       <c r="AS30" t="n">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>44768.10347222222</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>44767.26666666667</v>
+        <v>44767.27152777778</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>44767.61180555556</v>
@@ -5544,7 +5544,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>最近候选簇内有 4 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 5 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -5586,19 +5586,19 @@
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>33.69425785964816</v>
+        <v>33.69425785964818</v>
       </c>
       <c r="AB32" t="n">
-        <v>16.78510357618331</v>
+        <v>16.7851035761833</v>
       </c>
       <c r="AC32" t="n">
         <v>2.014921716170162</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.007390523789055</v>
+        <v>2.007390523789058</v>
       </c>
       <c r="AE32" t="n">
-        <v>16.72236573224895</v>
+        <v>16.72236573224896</v>
       </c>
       <c r="AF32" t="n">
         <v>0.282640329550115</v>
@@ -5689,7 +5689,7 @@
         <v>44805.75208333333</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>44804.90625</v>
+        <v>44804.9125</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>44805.3125</v>
@@ -5712,13 +5712,13 @@
         <v>1</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>44804.90763888889</v>
+        <v>44804.9125</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>44805.3125</v>
       </c>
       <c r="R33" t="n">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5747,61 +5747,61 @@
         <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>42.6394622892976</v>
+        <v>42.85279652219677</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.312351527773302</v>
+        <v>9.333301590214603</v>
       </c>
       <c r="AC33" t="n">
         <v>11.54690849701565</v>
       </c>
       <c r="AD33" t="n">
-        <v>5.129650995489094</v>
+        <v>4.59138667147811</v>
       </c>
       <c r="AE33" t="n">
-        <v>3.692716738884523</v>
+        <v>3.711192180424074</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.395217224328622</v>
+        <v>2.384255631866064</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.2805938199255909</v>
+        <v>0.4642133076582403</v>
       </c>
       <c r="AH33" t="n">
         <v>0.01233093894803119</v>
       </c>
       <c r="AI33" t="n">
-        <v>8.536243688345653</v>
+        <v>5.136120814574714</v>
       </c>
       <c r="AJ33" t="n">
-        <v>194.2445124757554</v>
+        <v>193.3555621282793</v>
       </c>
       <c r="AK33" t="n">
-        <v>27.67096554790823</v>
+        <v>27.79370943278385</v>
       </c>
       <c r="AL33" t="n">
-        <v>5.135673504259627</v>
+        <v>5.633373261988163</v>
       </c>
       <c r="AM33" t="n">
         <v>37.84305052757263</v>
       </c>
       <c r="AN33" t="n">
-        <v>5.387991570133382</v>
+        <v>4.933759603739577</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.7312033560229779</v>
+        <v>0.7344468547146646</v>
       </c>
       <c r="AP33" t="n">
-        <v>90</v>
+        <v>95.83333333333334</v>
       </c>
       <c r="AQ33" s="2" t="n">
-        <v>44804.90763888889</v>
+        <v>44804.9125</v>
       </c>
       <c r="AR33" s="2" t="n">
         <v>44805.3125</v>
       </c>
       <c r="AS33" t="n">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44812.17361111111</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>44810.41736111111</v>
+        <v>44810.43472222222</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>44811.46041666667</v>
@@ -5873,13 +5873,13 @@
         <v>1</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>44810.41736111111</v>
+        <v>44810.43472222222</v>
       </c>
       <c r="Q34" s="2" t="n">
         <v>44811.46041666667</v>
       </c>
       <c r="R34" t="n">
-        <v>1502</v>
+        <v>1477</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5908,61 +5908,61 @@
         <v>2</v>
       </c>
       <c r="AA34" t="n">
-        <v>18.14262754351979</v>
+        <v>18.3607474837428</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.821307260857689</v>
+        <v>4.143837509552638</v>
       </c>
       <c r="AC34" t="n">
         <v>8.333700877115948</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.747754185945178</v>
+        <v>4.430856046217169</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.177019287233937</v>
+        <v>2.20319252568337</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.547555963325688</v>
+        <v>1.55118712316063</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.5530143020648584</v>
+        <v>0.7216354903089144</v>
       </c>
       <c r="AH34" t="n">
         <v>0.2325780507824898</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.798401338893743</v>
+        <v>2.149543840334966</v>
       </c>
       <c r="AJ34" t="n">
-        <v>6.653920944470309</v>
+        <v>6.669533595030949</v>
       </c>
       <c r="AK34" t="n">
-        <v>12.06219644737138</v>
+        <v>12.0786600878983</v>
       </c>
       <c r="AL34" t="n">
-        <v>9.277646460135777</v>
+        <v>9.494526950580378</v>
       </c>
       <c r="AM34" t="n">
         <v>8.840900500615438</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.300135384464182</v>
+        <v>1.272170814909316</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.364362877574711</v>
+        <v>1.366225090651962</v>
       </c>
       <c r="AP34" t="n">
         <v>95</v>
       </c>
       <c r="AQ34" s="2" t="n">
-        <v>44810.41736111111</v>
+        <v>44810.43472222222</v>
       </c>
       <c r="AR34" s="2" t="n">
         <v>44811.46041666667</v>
       </c>
       <c r="AS34" t="n">
-        <v>1502</v>
+        <v>1477</v>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44813.23472222222</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>44812.87638888889</v>
+        <v>44812.87847222222</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>44813.01805555556</v>
@@ -6034,13 +6034,13 @@
         <v>1</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>44812.87638888889</v>
+        <v>44812.87847222222</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>44813.01805555556</v>
+        <v>44813.01527777778</v>
       </c>
       <c r="R35" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -6069,61 +6069,61 @@
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>15.55269539764984</v>
+        <v>15.55667708557162</v>
       </c>
       <c r="AB35" t="n">
-        <v>6.999247899055482</v>
+        <v>7.261327607896592</v>
       </c>
       <c r="AC35" t="n">
-        <v>12.79371216562062</v>
+        <v>12.90867313649922</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.222052372191105</v>
+        <v>2.142401214435491</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.215651501011817</v>
+        <v>1.205133705150932</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.9269978391786209</v>
+        <v>0.9354365739446464</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.4503539201690437</v>
+        <v>0.4666600895031399</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.4437715691592717</v>
+        <v>0.4438658770951951</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.058376307306629</v>
+        <v>2.004535195929483</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.088907680442045</v>
+        <v>2.107475753861622</v>
       </c>
       <c r="AK35" t="n">
-        <v>8.706083184290751</v>
+        <v>8.749853592763092</v>
       </c>
       <c r="AL35" t="n">
-        <v>4.435615418416758</v>
+        <v>4.545001892310878</v>
       </c>
       <c r="AM35" t="n">
-        <v>3.276422173242706</v>
+        <v>3.434516912163235</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.962767815294115</v>
+        <v>1.92515950489831</v>
       </c>
       <c r="AO35" t="n">
-        <v>2.657192121146665</v>
+        <v>2.547622800102034</v>
       </c>
       <c r="AP35" t="n">
         <v>100</v>
       </c>
       <c r="AQ35" s="2" t="n">
-        <v>44812.87638888889</v>
+        <v>44812.87847222222</v>
       </c>
       <c r="AR35" s="2" t="n">
-        <v>44813.01805555556</v>
+        <v>44813.01527777778</v>
       </c>
       <c r="AS35" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>44818.1875</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>44817.71597222222</v>
+        <v>44817.71944444445</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>44817.93055555555</v>
@@ -6233,13 +6233,13 @@
         <v>48.91903269732514</v>
       </c>
       <c r="AB36" t="n">
-        <v>54.91549614164563</v>
+        <v>54.91549614164565</v>
       </c>
       <c r="AC36" t="n">
         <v>50.31185591803666</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.8908056219895824</v>
+        <v>0.890805621989582</v>
       </c>
       <c r="AE36" t="n">
         <v>0.9723162027061658</v>
@@ -6248,13 +6248,13 @@
         <v>0.5937637022849205</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.8064629497623312</v>
+        <v>0.8064629497623308</v>
       </c>
       <c r="AH36" t="n">
         <v>0.5349059541064629</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.7362566407544273</v>
+        <v>0.7362566407544278</v>
       </c>
       <c r="AJ36" t="n">
         <v>1.110033825061411</v>
@@ -6810,7 +6810,7 @@
         <v>44921.89791666667</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>44921.22291666667</v>
+        <v>44921.22638888889</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>44921.47708333333</v>
@@ -7289,7 +7289,7 @@
         <v>44966.70069444444</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>44964.53194444445</v>
+        <v>44964.53958333333</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>44965.25625</v>
@@ -7450,7 +7450,7 @@
         <v>44975.22083333333</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>44974.58541666667</v>
+        <v>44974.59375</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>44975.02361111111</v>
@@ -7473,13 +7473,13 @@
         <v>1</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>44974.58958333333</v>
+        <v>44974.59444444445</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>44975.00694444445</v>
+        <v>44975.00486111111</v>
       </c>
       <c r="R44" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -7508,49 +7508,49 @@
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>25.79142714834222</v>
+        <v>25.98524109971136</v>
       </c>
       <c r="AB44" t="n">
-        <v>7.147739557336881</v>
+        <v>7.40900368690491</v>
       </c>
       <c r="AC44" t="n">
-        <v>24.1021541319952</v>
+        <v>24.13971360630449</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.608333367696408</v>
+        <v>3.50725174366415</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.070088051345774</v>
+        <v>1.076451921655147</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.9784296809279239</v>
+        <v>0.988532870052566</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.4890492044354503</v>
+        <v>0.4939113085744034</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.2124822092214449</v>
+        <v>0.210674626629923</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.000677379809678</v>
+        <v>2.001438017092196</v>
       </c>
       <c r="AJ44" t="n">
-        <v>4.604760485656582</v>
+        <v>4.692225570139733</v>
       </c>
       <c r="AK44" t="n">
-        <v>8.274529483863548</v>
+        <v>8.253141494162142</v>
       </c>
       <c r="AL44" t="n">
-        <v>6.855976299444834</v>
+        <v>7.141403003533681</v>
       </c>
       <c r="AM44" t="n">
-        <v>7.222091035048167</v>
+        <v>7.178038732210795</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.206907539125184</v>
+        <v>1.155675080943948</v>
       </c>
       <c r="AO44" t="n">
-        <v>1.145724893761099</v>
+        <v>1.149776673275239</v>
       </c>
       <c r="AP44" t="n">
         <v>100</v>
@@ -7611,7 +7611,7 @@
         <v>44977.18263888889</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>44976.41527777778</v>
+        <v>44976.42152777778</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>44976.8</v>
@@ -7634,13 +7634,13 @@
         <v>1</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>44976.41527777778</v>
+        <v>44976.42152777778</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>44976.8</v>
       </c>
       <c r="R45" t="n">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -7669,61 +7669,61 @@
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>28.55881347403808</v>
+        <v>28.75891993589782</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.18664306243261</v>
+        <v>8.807637350294327</v>
       </c>
       <c r="AC45" t="n">
         <v>17.76632777796855</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.48846447270806</v>
+        <v>3.265225257592693</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.607468568122048</v>
+        <v>1.618731810833797</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.207364286396679</v>
+        <v>1.214268147747312</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.337611784756062</v>
+        <v>0.3643843174059034</v>
       </c>
       <c r="AH45" t="n">
         <v>0.245878419832268</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.576191178483439</v>
+        <v>3.332383117890024</v>
       </c>
       <c r="AJ45" t="n">
-        <v>4.910411768630659</v>
+        <v>4.938490122783672</v>
       </c>
       <c r="AK45" t="n">
-        <v>14.43416590655108</v>
+        <v>14.57050186532353</v>
       </c>
       <c r="AL45" t="n">
-        <v>4.542871099462112</v>
+        <v>4.404693913211426</v>
       </c>
       <c r="AM45" t="n">
         <v>4.776556350290775</v>
       </c>
       <c r="AN45" t="n">
-        <v>3.177322356397065</v>
+        <v>3.307948782007488</v>
       </c>
       <c r="AO45" t="n">
-        <v>3.021877027719435</v>
+        <v>3.050419757831716</v>
       </c>
       <c r="AP45" t="n">
-        <v>98.55595667870037</v>
+        <v>98.53211009174312</v>
       </c>
       <c r="AQ45" s="2" t="n">
-        <v>44976.41527777778</v>
+        <v>44976.42152777778</v>
       </c>
       <c r="AR45" s="2" t="n">
         <v>44976.8</v>
       </c>
       <c r="AS45" t="n">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>44999.35069444445</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>44999.04722222222</v>
+        <v>44999.04861111111</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>44999.15625</v>
@@ -8251,7 +8251,7 @@
         <v>45006.82569444444</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45006.51597222222</v>
+        <v>45006.51736111111</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>45006.61180555556</v>
@@ -8274,13 +8274,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>45006.51597222222</v>
+        <v>45006.51736111111</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>45006.61180555556</v>
       </c>
       <c r="R49" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -8309,49 +8309,49 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>60.91672931523711</v>
+        <v>61.1205706119537</v>
       </c>
       <c r="AB49" t="n">
-        <v>27.2216555066525</v>
+        <v>27.56154886815282</v>
       </c>
       <c r="AC49" t="n">
-        <v>66.78570482254037</v>
+        <v>66.78570482254035</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.237803990295525</v>
+        <v>2.217602896859621</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.9121222794174592</v>
+        <v>0.9151744489986329</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.9231419019793486</v>
+        <v>0.9303022455428802</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.1126496446191661</v>
+        <v>0.1182404433864568</v>
       </c>
       <c r="AH49" t="n">
         <v>0.07660620720759302</v>
       </c>
       <c r="AI49" t="n">
-        <v>8.19480527524262</v>
+        <v>7.867885292871263</v>
       </c>
       <c r="AJ49" t="n">
-        <v>12.0504843618971</v>
+        <v>12.14395385770607</v>
       </c>
       <c r="AK49" t="n">
-        <v>15.88472978727541</v>
+        <v>15.89102117563872</v>
       </c>
       <c r="AL49" t="n">
-        <v>18.99270341396332</v>
+        <v>18.92221562067668</v>
       </c>
       <c r="AM49" t="n">
         <v>20.11946125030518</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.8363595977388377</v>
+        <v>0.8398076363887476</v>
       </c>
       <c r="AO49" t="n">
-        <v>0.7895206332641969</v>
+        <v>0.789833334895967</v>
       </c>
       <c r="AP49" t="n">
         <v>93.33333333333333</v>
@@ -8412,7 +8412,7 @@
         <v>45026.55277777778</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45026.19027777778</v>
+        <v>45026.19513888889</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>45026.45</v>
@@ -8473,31 +8473,31 @@
         <v>255.5529112904502</v>
       </c>
       <c r="AB50" t="n">
-        <v>127.6885130294571</v>
+        <v>127.688513029457</v>
       </c>
       <c r="AC50" t="n">
         <v>116.3955503234934</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.001377455398008</v>
+        <v>2.001377455398009</v>
       </c>
       <c r="AE50" t="n">
         <v>2.195555677001418</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.6175788557033267</v>
+        <v>0.6175788557033273</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.9151809195287418</v>
+        <v>0.9151809195287416</v>
       </c>
       <c r="AH50" t="n">
         <v>0.03006164887019734</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.6748161402024633</v>
+        <v>0.6748161402024641</v>
       </c>
       <c r="AJ50" t="n">
-        <v>20.54374523400095</v>
+        <v>20.54374523400097</v>
       </c>
       <c r="AK50" t="n">
         <v>38.93565937661781</v>
@@ -8573,7 +8573,7 @@
         <v>45038.51597222222</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45038.33472222222</v>
+        <v>45038.33611111111</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>45038.40277777778</v>
@@ -8634,7 +8634,7 @@
         <v>137.2651116561891</v>
       </c>
       <c r="AB51" t="n">
-        <v>102.2028174485101</v>
+        <v>102.20281744851</v>
       </c>
       <c r="AC51" t="n">
         <v>120.6608615536161</v>
@@ -8649,16 +8649,16 @@
         <v>0.6596516445953327</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.6829261793006371</v>
+        <v>0.6829261793006373</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.7849646005223108</v>
+        <v>0.7849646005223104</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.9659193988885604</v>
+        <v>0.9659193988885603</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.8403584622241619</v>
+        <v>0.8403584622241623</v>
       </c>
       <c r="AK51" t="n">
         <v>5.65581691339612</v>
@@ -8734,7 +8734,7 @@
         <v>45049.43263888889</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45048.91944444444</v>
+        <v>45048.92083333333</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>45049.06736111111</v>
@@ -8795,13 +8795,13 @@
         <v>29.36703203292122</v>
       </c>
       <c r="AB52" t="n">
-        <v>29.30239192008973</v>
+        <v>29.30239192008972</v>
       </c>
       <c r="AC52" t="n">
         <v>17.23162261130171</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.00220596711039</v>
+        <v>1.002205967110391</v>
       </c>
       <c r="AE52" t="n">
         <v>1.70425227474865</v>
@@ -8895,7 +8895,7 @@
         <v>45075.51111111111</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45075.02708333333</v>
+        <v>45075.03402777778</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>45075.38194444445</v>
@@ -8956,31 +8956,31 @@
         <v>19.97723364519432</v>
       </c>
       <c r="AB53" t="n">
-        <v>18.9801466582847</v>
+        <v>18.98014665828471</v>
       </c>
       <c r="AC53" t="n">
-        <v>12.36135874165429</v>
+        <v>12.36135874165432</v>
       </c>
       <c r="AD53" t="n">
         <v>1.052533155030938</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.61610338011441</v>
+        <v>1.616103380114408</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.2299866473068754</v>
+        <v>0.2299866473068753</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.07772822798078638</v>
+        <v>0.07772822798078585</v>
       </c>
       <c r="AH53" t="n">
         <v>0.06741303964477012</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.958856174667017</v>
+        <v>2.958856174667036</v>
       </c>
       <c r="AJ53" t="n">
-        <v>3.411604765469401</v>
+        <v>3.4116047654694</v>
       </c>
       <c r="AK53" t="n">
         <v>6.962839192237127</v>
@@ -9056,7 +9056,7 @@
         <v>45104.84444444445</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45103.01111111111</v>
+        <v>45103.03055555555</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>45104.15</v>
@@ -9114,25 +9114,25 @@
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>25.54373198424315</v>
+        <v>25.54373198424314</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.94584141912624</v>
+        <v>14.94584141912623</v>
       </c>
       <c r="AC54" t="n">
         <v>12.08595239294918</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.709086244656306</v>
+        <v>1.709086244656307</v>
       </c>
       <c r="AE54" t="n">
         <v>2.113505924377551</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.6100281104826893</v>
+        <v>0.6100281104826891</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.2997097486260761</v>
+        <v>0.299709748626076</v>
       </c>
       <c r="AH54" t="n">
         <v>0.05754223638210192</v>
@@ -9141,7 +9141,7 @@
         <v>2.03539629017464</v>
       </c>
       <c r="AJ54" t="n">
-        <v>10.60139731851705</v>
+        <v>10.60139731851704</v>
       </c>
       <c r="AK54" t="n">
         <v>7.054474005701751</v>
@@ -9217,7 +9217,7 @@
         <v>45105.26458333333</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45104.84513888889</v>
+        <v>45104.84791666667</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>45105.03472222222</v>
@@ -9278,10 +9278,10 @@
         <v>36.81740379333498</v>
       </c>
       <c r="AB55" t="n">
-        <v>17.95654768466949</v>
+        <v>17.9565476846695</v>
       </c>
       <c r="AC55" t="n">
-        <v>18.3922272499692</v>
+        <v>18.39222724996921</v>
       </c>
       <c r="AD55" t="n">
         <v>2.050360929053642</v>
@@ -9378,7 +9378,7 @@
         <v>45125.51597222222</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45125.25625</v>
+        <v>45125.25694444445</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>45125.32013888889</v>
@@ -9454,13 +9454,13 @@
         <v>0.3527207132834273</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.8825055308326971</v>
+        <v>0.8825055308326981</v>
       </c>
       <c r="AH56" t="n">
         <v>0.08900366631857111</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.399681022906014</v>
+        <v>0.3996810229060136</v>
       </c>
       <c r="AJ56" t="n">
         <v>3.962990828051205</v>
@@ -9539,7 +9539,7 @@
         <v>45126.09930555556</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45125.71319444444</v>
+        <v>45125.71458333333</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>45125.84166666667</v>
@@ -9562,13 +9562,13 @@
         <v>1</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>45125.71319444444</v>
+        <v>45125.71458333333</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>45125.82013888889</v>
+        <v>45125.81597222222</v>
       </c>
       <c r="R57" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -9577,7 +9577,7 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -9597,61 +9597,61 @@
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>59.81702021193281</v>
+        <v>60.7972433556496</v>
       </c>
       <c r="AB57" t="n">
-        <v>29.90342555681864</v>
+        <v>30.39250251664055</v>
       </c>
       <c r="AC57" t="n">
-        <v>24.56552167097725</v>
+        <v>25.25479877312976</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.000340064661696</v>
+        <v>2.0004026757047</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.434998979997367</v>
+        <v>2.407354099385491</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.8930258102634012</v>
+        <v>0.8960039480716346</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.204901761310599</v>
+        <v>1.2381601466897</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.4076881270793175</v>
+        <v>0.3755498344481642</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.7411606812592229</v>
+        <v>0.7236575579234705</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.190463128423799</v>
+        <v>2.385845674484798</v>
       </c>
       <c r="AK57" t="n">
-        <v>17.22662720180951</v>
+        <v>17.3065421162811</v>
       </c>
       <c r="AL57" t="n">
-        <v>12.84125141178568</v>
+        <v>12.90878032719096</v>
       </c>
       <c r="AM57" t="n">
-        <v>4.12676657307893</v>
+        <v>4.375510476715863</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.341506886626247</v>
+        <v>1.340679884359542</v>
       </c>
       <c r="AO57" t="n">
-        <v>4.174364335067524</v>
+        <v>3.955319546913968</v>
       </c>
       <c r="AP57" t="n">
         <v>100</v>
       </c>
       <c r="AQ57" s="2" t="n">
-        <v>45125.71319444444</v>
+        <v>45125.71458333333</v>
       </c>
       <c r="AR57" s="2" t="n">
-        <v>45125.82013888889</v>
+        <v>45125.81597222222</v>
       </c>
       <c r="AS57" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>45131.79791666667</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45131.50555555556</v>
+        <v>45131.50625</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>45131.58194444444</v>
@@ -9938,7 +9938,7 @@
         <v>0.9020772518253484</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.5113883397846466</v>
+        <v>0.5113883397846465</v>
       </c>
       <c r="AI59" t="n">
         <v>1.01999580376138</v>
@@ -10020,7 +10020,7 @@
         <v>45134.18055555555</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45133.91666666666</v>
+        <v>45133.91944444444</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>45134.06805555556</v>
@@ -10043,13 +10043,13 @@
         <v>1</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>45133.91666666666</v>
+        <v>45133.91944444444</v>
       </c>
       <c r="Q60" s="2" t="n">
         <v>45134.06805555556</v>
       </c>
       <c r="R60" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -10078,61 +10078,61 @@
         <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>22.90591652126295</v>
+        <v>23.13048710201934</v>
       </c>
       <c r="AB60" t="n">
-        <v>6.718938772148556</v>
+        <v>6.837625324461197</v>
       </c>
       <c r="AC60" t="n">
         <v>18.99820989608764</v>
       </c>
       <c r="AD60" t="n">
-        <v>3.40915690677416</v>
+        <v>3.38282459251919</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.205688148859753</v>
+        <v>1.217508766801375</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.704814450460234</v>
+        <v>1.727264630053636</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.7671348629317349</v>
+        <v>0.7355891015265097</v>
       </c>
       <c r="AH60" t="n">
         <v>0.4000419845635098</v>
       </c>
       <c r="AI60" t="n">
-        <v>2.222313875744088</v>
+        <v>2.34813787543777</v>
       </c>
       <c r="AJ60" t="n">
-        <v>4.261588823784022</v>
+        <v>4.317708382379599</v>
       </c>
       <c r="AK60" t="n">
-        <v>7.308510468025273</v>
+        <v>7.357578996673365</v>
       </c>
       <c r="AL60" t="n">
-        <v>3.292804983071983</v>
+        <v>3.297673949413002</v>
       </c>
       <c r="AM60" t="n">
         <v>16.09163762728373</v>
       </c>
       <c r="AN60" t="n">
-        <v>2.21953942173851</v>
+        <v>2.231142044222729</v>
       </c>
       <c r="AO60" t="n">
-        <v>0.4541806519203198</v>
+        <v>0.4572299704411952</v>
       </c>
       <c r="AP60" t="n">
         <v>100</v>
       </c>
       <c r="AQ60" s="2" t="n">
-        <v>45133.91666666666</v>
+        <v>45133.91944444444</v>
       </c>
       <c r="AR60" s="2" t="n">
         <v>45134.06805555556</v>
       </c>
       <c r="AS60" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45176.73680555556</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45175.84930555556</v>
+        <v>45175.85833333333</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>45176.37361111111</v>
@@ -10356,117 +10356,117 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 10 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>45175.84930555556</v>
+        <v>45176.29097222222</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>45176.31805555556</v>
+        <v>45176.37361111111</v>
       </c>
       <c r="R62" t="n">
-        <v>675</v>
+        <v>119</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U62" t="n">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="W62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X62" t="b">
         <v>0</v>
       </c>
       <c r="Y62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z62" t="n">
         <v>1</v>
       </c>
       <c r="AA62" t="n">
-        <v>90.12655733803255</v>
+        <v>24.31934783625715</v>
       </c>
       <c r="AB62" t="n">
-        <v>45.04510245853001</v>
+        <v>40.26027946125166</v>
       </c>
       <c r="AC62" t="n">
-        <v>20.63795811653193</v>
+        <v>17.61500444836068</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.000807022716976</v>
+        <v>0.6040531303232312</v>
       </c>
       <c r="AE62" t="n">
-        <v>4.367028793698207</v>
+        <v>1.380604126870964</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.4909221319047249</v>
+        <v>0.01207055441461246</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.990369444619792</v>
+        <v>0.09355175233017027</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.0119573987506565</v>
+        <v>0.01057279276675634</v>
       </c>
       <c r="AI62" t="n">
-        <v>0.2466487481667017</v>
+        <v>0.1290254229767081</v>
       </c>
       <c r="AJ62" t="n">
-        <v>41.05593048636698</v>
+        <v>1.141661875050221</v>
       </c>
       <c r="AK62" t="n">
-        <v>44.52882802775046</v>
+        <v>7.853457177331781</v>
       </c>
       <c r="AL62" t="n">
-        <v>3.391759600816294</v>
+        <v>38.11027010281881</v>
       </c>
       <c r="AM62" t="n">
-        <v>6.28564478600553</v>
+        <v>13.25144889975588</v>
       </c>
       <c r="AN62" t="n">
-        <v>13.12853305317797</v>
+        <v>0.2060719369383557</v>
       </c>
       <c r="AO62" t="n">
-        <v>7.084210060181928</v>
+        <v>0.5926489425225389</v>
       </c>
       <c r="AP62" t="n">
-        <v>98.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="AQ62" s="2" t="n">
-        <v>45175.84930555556</v>
+        <v>45176.29097222222</v>
       </c>
       <c r="AR62" s="2" t="n">
-        <v>45175.87638888889</v>
+        <v>45176.37361111111</v>
       </c>
       <c r="AS62" t="n">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="AU62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -10501,7 +10501,7 @@
         <v>45178.27916666667</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45177.81388888889</v>
+        <v>45177.81527777778</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>45177.95416666667</v>
@@ -10517,117 +10517,117 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="P63" s="2" t="n">
-        <v>45177.81388888889</v>
+        <v>45177.87361111111</v>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>45177.88680555556</v>
+        <v>45177.90486111111</v>
       </c>
       <c r="R63" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="W63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X63" t="b">
         <v>0</v>
       </c>
       <c r="Y63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z63" t="n">
         <v>1</v>
       </c>
       <c r="AA63" t="n">
-        <v>79.9656145719498</v>
+        <v>44.36713241859713</v>
       </c>
       <c r="AB63" t="n">
-        <v>39.81947305390329</v>
+        <v>70.72027353498676</v>
       </c>
       <c r="AC63" t="n">
-        <v>18.80260903782322</v>
+        <v>17.87440748956477</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.008203736490963</v>
+        <v>0.6273608712309039</v>
       </c>
       <c r="AE63" t="n">
-        <v>4.252899925275872</v>
+        <v>2.48215961533265</v>
       </c>
       <c r="AF63" t="n">
-        <v>4.799559651457354</v>
+        <v>0.08124699178716178</v>
       </c>
       <c r="AG63" t="n">
-        <v>3.741474825323444</v>
+        <v>4.564410616731218</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.04222999443428534</v>
+        <v>0.04889748782409432</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.282798862890235</v>
+        <v>0.01780010577693084</v>
       </c>
       <c r="AJ63" t="n">
-        <v>113.6528601472115</v>
+        <v>1.661578036062769</v>
       </c>
       <c r="AK63" t="n">
-        <v>30.19166884010746</v>
+        <v>13.6345793813467</v>
       </c>
       <c r="AL63" t="n">
-        <v>6.603404056715468</v>
+        <v>26.58669432997704</v>
       </c>
       <c r="AM63" t="n">
-        <v>20.73552325864633</v>
+        <v>22.93095863660177</v>
       </c>
       <c r="AN63" t="n">
-        <v>4.572137125154931</v>
+        <v>0.5128346988957344</v>
       </c>
       <c r="AO63" t="n">
-        <v>1.45603602395315</v>
+        <v>0.5945926464488738</v>
       </c>
       <c r="AP63" t="n">
         <v>100</v>
       </c>
       <c r="AQ63" s="2" t="n">
-        <v>45177.81388888889</v>
+        <v>45177.87361111111</v>
       </c>
       <c r="AR63" s="2" t="n">
-        <v>45177.85902777778</v>
+        <v>45177.90486111111</v>
       </c>
       <c r="AS63" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="AU63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -10662,7 +10662,7 @@
         <v>45179.05555555555</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45178.44513888889</v>
+        <v>45178.45208333333</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>45178.83333333334</v>
@@ -10726,16 +10726,16 @@
         <v>25.61711818377177</v>
       </c>
       <c r="AC64" t="n">
-        <v>29.35653855959573</v>
+        <v>29.35653855959571</v>
       </c>
       <c r="AD64" t="n">
         <v>0.9128080859715902</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.7965350741187227</v>
+        <v>0.7965350741187235</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.3797414409829487</v>
+        <v>0.3797414409829488</v>
       </c>
       <c r="AG64" t="n">
         <v>0.396335194109053</v>
@@ -10744,7 +10744,7 @@
         <v>0.3050433751919703</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.9581320221551194</v>
+        <v>0.9581320221551195</v>
       </c>
       <c r="AJ64" t="n">
         <v>1.244876866261952</v>
@@ -10823,7 +10823,7 @@
         <v>45188.51111111111</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45188.1</v>
+        <v>45188.10347222222</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>45188.30625</v>
@@ -10846,13 +10846,13 @@
         <v>1</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>45188.1</v>
+        <v>45188.10347222222</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>45188.26388888889</v>
+        <v>45188.25902777778</v>
       </c>
       <c r="R65" t="n">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -10861,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -10881,61 +10881,61 @@
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>172.4180416369814</v>
+        <v>174.9521060844035</v>
       </c>
       <c r="AB65" t="n">
-        <v>73.99207621892296</v>
+        <v>78.11561890708077</v>
       </c>
       <c r="AC65" t="n">
-        <v>89.4321864106918</v>
+        <v>90.66241622924784</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.330223051544629</v>
+        <v>2.239655891256658</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.927919338181008</v>
+        <v>1.929709281539792</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.431139614282191</v>
+        <v>1.476385203133349</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.7146420879790861</v>
+        <v>0.7361207233091501</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.3352013887916106</v>
+        <v>0.3275690948387241</v>
       </c>
       <c r="AI65" t="n">
-        <v>2.002596318290273</v>
+        <v>2.005629180627359</v>
       </c>
       <c r="AJ65" t="n">
-        <v>4.269491899903518</v>
+        <v>4.507095530059804</v>
       </c>
       <c r="AK65" t="n">
-        <v>8.974299008942257</v>
+        <v>8.494852383621037</v>
       </c>
       <c r="AL65" t="n">
-        <v>5.561670231819153</v>
+        <v>5.801095147927602</v>
       </c>
       <c r="AM65" t="n">
-        <v>18.54147334098816</v>
+        <v>18.98705094655355</v>
       </c>
       <c r="AN65" t="n">
-        <v>1.613597828508232</v>
+        <v>1.464353224176259</v>
       </c>
       <c r="AO65" t="n">
-        <v>0.4840121841398379</v>
+        <v>0.4474024116506091</v>
       </c>
       <c r="AP65" t="n">
-        <v>99.57627118644068</v>
+        <v>99.55357142857143</v>
       </c>
       <c r="AQ65" s="2" t="n">
-        <v>45188.1</v>
+        <v>45188.10347222222</v>
       </c>
       <c r="AR65" s="2" t="n">
-        <v>45188.26388888889</v>
+        <v>45188.25902777778</v>
       </c>
       <c r="AS65" t="n">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45189.53819444445</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45189.03263888889</v>
+        <v>45189.03680555556</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>45189.29097222222</v>
@@ -11042,34 +11042,34 @@
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>79.16177080713108</v>
+        <v>79.16177080713098</v>
       </c>
       <c r="AB66" t="n">
-        <v>84.37503994623822</v>
+        <v>84.3750399462382</v>
       </c>
       <c r="AC66" t="n">
         <v>35.50421591546795</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.9382131357516522</v>
+        <v>0.9382131357516512</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.22964424832272</v>
+        <v>2.229644248322717</v>
       </c>
       <c r="AF66" t="n">
         <v>0.8275759870115478</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.4059678472573043</v>
+        <v>0.4059678472573044</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.1662143443323705</v>
+        <v>0.1662143443323707</v>
       </c>
       <c r="AI66" t="n">
         <v>2.038525938944682</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4.978968514033216</v>
+        <v>4.978968514033208</v>
       </c>
       <c r="AK66" t="n">
         <v>28.52096035986236</v>
@@ -11145,7 +11145,7 @@
         <v>45210.38819444444</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45209.93888888889</v>
+        <v>45209.94305555556</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>45210.19236111111</v>
@@ -11168,13 +11168,13 @@
         <v>1</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>45209.93888888889</v>
+        <v>45209.94305555556</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>45210.17708333334</v>
+        <v>45210.14861111111</v>
       </c>
       <c r="R67" t="n">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -11183,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -11203,61 +11203,61 @@
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>161.2094277498688</v>
+        <v>177.3147020311569</v>
       </c>
       <c r="AB67" t="n">
-        <v>80.42339791403874</v>
+        <v>88.63209317525228</v>
       </c>
       <c r="AC67" t="n">
-        <v>35.10055469228539</v>
+        <v>33.82390339957328</v>
       </c>
       <c r="AD67" t="n">
-        <v>2.004509035071844</v>
+        <v>2.00056994795951</v>
       </c>
       <c r="AE67" t="n">
-        <v>4.592788608702539</v>
+        <v>5.242289748065976</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.719734844944747</v>
+        <v>0.7929747737590471</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.7738245593981629</v>
+        <v>0.8121174648961779</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.03537438891759347</v>
+        <v>0.04044135016112544</v>
       </c>
       <c r="AI67" t="n">
-        <v>0.9301008041209189</v>
+        <v>0.9764286670776401</v>
       </c>
       <c r="AJ67" t="n">
-        <v>20.34621281010416</v>
+        <v>19.60801928223703</v>
       </c>
       <c r="AK67" t="n">
-        <v>44.97243260116515</v>
+        <v>49.0803769169929</v>
       </c>
       <c r="AL67" t="n">
-        <v>11.81737742694095</v>
+        <v>14.59136289230858</v>
       </c>
       <c r="AM67" t="n">
-        <v>20.11273156007131</v>
+        <v>19.37042027711868</v>
       </c>
       <c r="AN67" t="n">
-        <v>3.805618706790068</v>
+        <v>3.363659534700779</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.236018139398152</v>
+        <v>2.533779660680317</v>
       </c>
       <c r="AP67" t="n">
-        <v>99.16666666666667</v>
+        <v>99.66216216216216</v>
       </c>
       <c r="AQ67" s="2" t="n">
-        <v>45209.93888888889</v>
+        <v>45209.94305555556</v>
       </c>
       <c r="AR67" s="2" t="n">
-        <v>45210.17708333334</v>
+        <v>45210.14861111111</v>
       </c>
       <c r="AS67" t="n">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45217.49305555555</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45216.43333333333</v>
+        <v>45216.43958333333</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>45216.89027777778</v>
@@ -11329,13 +11329,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>45216.43333333333</v>
+        <v>45216.43958333333</v>
       </c>
       <c r="Q68" s="2" t="n">
         <v>45216.89027777778</v>
       </c>
       <c r="R68" t="n">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -11364,52 +11364,52 @@
         <v>2</v>
       </c>
       <c r="AA68" t="n">
-        <v>132.6623048078055</v>
+        <v>133.4372404404546</v>
       </c>
       <c r="AB68" t="n">
-        <v>33.97354589250353</v>
+        <v>37.22887869622971</v>
       </c>
       <c r="AC68" t="n">
         <v>56.204403738446</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.90487072581606</v>
+        <v>3.584240114488546</v>
       </c>
       <c r="AE68" t="n">
-        <v>2.36035427802358</v>
+        <v>2.37414208789441</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.185956407148662</v>
+        <v>1.188009208032963</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.3728996984499459</v>
+        <v>0.4247502105148881</v>
       </c>
       <c r="AH68" t="n">
         <v>0.02846251035819402</v>
       </c>
       <c r="AI68" t="n">
-        <v>3.180363009351835</v>
+        <v>2.796959668584605</v>
       </c>
       <c r="AJ68" t="n">
-        <v>41.66731578570121</v>
+        <v>41.73943875934151</v>
       </c>
       <c r="AK68" t="n">
-        <v>28.33181392929961</v>
+        <v>28.51562463374771</v>
       </c>
       <c r="AL68" t="n">
-        <v>6.49457974769175</v>
+        <v>7.213118210310737</v>
       </c>
       <c r="AM68" t="n">
         <v>12.00703600160778</v>
       </c>
       <c r="AN68" t="n">
-        <v>4.36237832622951</v>
+        <v>3.953300611791759</v>
       </c>
       <c r="AO68" t="n">
-        <v>2.359600981083583</v>
+        <v>2.374909563853176</v>
       </c>
       <c r="AP68" t="n">
-        <v>98.63221884498479</v>
+        <v>98.61325115562404</v>
       </c>
       <c r="AQ68" s="2" t="n">
         <v>45216.54583333333</v>
@@ -11467,7 +11467,7 @@
         <v>45227.87083333333</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45227.25416666667</v>
+        <v>45227.26111111111</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>45227.64652777778</v>
@@ -11628,7 +11628,7 @@
         <v>45242.84791666667</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45241.38472222222</v>
+        <v>45241.40069444444</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>45242.30069444444</v>
@@ -11686,10 +11686,10 @@
         <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>34.13807357395296</v>
+        <v>34.13807357395297</v>
       </c>
       <c r="AB70" t="n">
-        <v>45.20875063814276</v>
+        <v>45.20875063814277</v>
       </c>
       <c r="AC70" t="n">
         <v>29.49773746622809</v>
@@ -11701,7 +11701,7 @@
         <v>1.157311594254901</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.7502806299762316</v>
+        <v>0.7502806299762307</v>
       </c>
       <c r="AG70" t="n">
         <v>1.335454960049715</v>
@@ -11710,10 +11710,10 @@
         <v>0.2701421690795778</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.5618164988119858</v>
+        <v>0.5618164988119851</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.777354725967332</v>
+        <v>2.777354725967329</v>
       </c>
       <c r="AK70" t="n">
         <v>7.972305303106326</v>
@@ -11789,7 +11789,7 @@
         <v>45261.02013888889</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45260.44930555556</v>
+        <v>45260.45555555556</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>45260.78680555556</v>
@@ -11812,13 +11812,13 @@
         <v>1</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>45260.44930555556</v>
+        <v>45260.45555555556</v>
       </c>
       <c r="Q71" s="2" t="n">
         <v>45260.78680555556</v>
       </c>
       <c r="R71" t="n">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -11847,61 +11847,61 @@
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>27.27060212596914</v>
+        <v>27.35198975355786</v>
       </c>
       <c r="AB71" t="n">
-        <v>8.874165247199274</v>
+        <v>10.07436807932863</v>
       </c>
       <c r="AC71" t="n">
         <v>18.92261337316835</v>
       </c>
       <c r="AD71" t="n">
-        <v>3.073032940712465</v>
+        <v>2.715007982454086</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.441164684188811</v>
+        <v>1.445465761739977</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.132603163708709</v>
+        <v>1.148407839639057</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.4189872960317321</v>
+        <v>0.4123317550367037</v>
       </c>
       <c r="AH71" t="n">
         <v>0.5402416200940497</v>
       </c>
       <c r="AI71" t="n">
-        <v>2.703192135980492</v>
+        <v>2.785154976814317</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2.096475209576663</v>
+        <v>2.125730038050627</v>
       </c>
       <c r="AK71" t="n">
-        <v>9.383526427043725</v>
+        <v>9.48930150672766</v>
       </c>
       <c r="AL71" t="n">
-        <v>2.528903736771584</v>
+        <v>2.626117173124294</v>
       </c>
       <c r="AM71" t="n">
         <v>13.5209586540858</v>
       </c>
       <c r="AN71" t="n">
-        <v>3.710511511609691</v>
+        <v>3.613434161979235</v>
       </c>
       <c r="AO71" t="n">
-        <v>0.6939986037312663</v>
+        <v>0.7018216495958414</v>
       </c>
       <c r="AP71" t="n">
-        <v>98.35390946502058</v>
+        <v>98.32285115303984</v>
       </c>
       <c r="AQ71" s="2" t="n">
-        <v>45260.44930555556</v>
+        <v>45260.45555555556</v>
       </c>
       <c r="AR71" s="2" t="n">
         <v>45260.78680555556</v>
       </c>
       <c r="AS71" t="n">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45261.43541666667</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45261.10208333333</v>
+        <v>45261.10277777778</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>45261.19305555556</v>
@@ -12014,7 +12014,7 @@
         <v>32.57613972836707</v>
       </c>
       <c r="AC72" t="n">
-        <v>39.88001037773662</v>
+        <v>39.88001037773663</v>
       </c>
       <c r="AD72" t="n">
         <v>1.371598606107302</v>
@@ -12026,16 +12026,16 @@
         <v>1.440391497114222</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.7136270793232579</v>
+        <v>0.7136270793232576</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.2893407870751676</v>
+        <v>0.2893407870751673</v>
       </c>
       <c r="AI72" t="n">
-        <v>2.018409248819656</v>
+        <v>2.018409248819657</v>
       </c>
       <c r="AJ72" t="n">
-        <v>4.978183379103148</v>
+        <v>4.978183379103152</v>
       </c>
       <c r="AK72" t="n">
         <v>8.171018833205814</v>
@@ -12429,7 +12429,7 @@
         <v>45289.61458333334</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45289.10277777778</v>
+        <v>45289.11041666667</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>45289.50625</v>
@@ -12508,13 +12508,13 @@
         <v>1.263335023274878</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.6030205248179986</v>
+        <v>0.6030205248180006</v>
       </c>
       <c r="AI75" t="n">
         <v>1.377366718698222</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.885599318779146</v>
+        <v>2.885599318779136</v>
       </c>
       <c r="AK75" t="n">
         <v>3.340026118556658</v>
@@ -12590,7 +12590,7 @@
         <v>45370.41944444444</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45369.70555555556</v>
+        <v>45369.71111111111</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>45370.05763888889</v>
@@ -12648,7 +12648,7 @@
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>86.22753305462703</v>
+        <v>86.22753305462712</v>
       </c>
       <c r="AB76" t="n">
         <v>100.6060252070562</v>
@@ -12657,10 +12657,10 @@
         <v>114.6259381365307</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.8570812024146967</v>
+        <v>0.8570812024146978</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.7522514926065128</v>
+        <v>0.7522514926065135</v>
       </c>
       <c r="AF76" t="n">
         <v>0.1763021173839961</v>
@@ -12751,7 +12751,7 @@
         <v>45375.09027777778</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45374.56388888889</v>
+        <v>45374.56527777778</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>45374.72083333333</v>
@@ -12774,13 +12774,13 @@
         <v>1</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>45374.56388888889</v>
+        <v>45374.56527777778</v>
       </c>
       <c r="Q77" s="2" t="n">
         <v>45374.66944444444</v>
       </c>
       <c r="R77" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -12809,61 +12809,61 @@
         <v>1</v>
       </c>
       <c r="AA77" t="n">
-        <v>83.79591901685757</v>
+        <v>82.65505936994668</v>
       </c>
       <c r="AB77" t="n">
-        <v>51.81348636673869</v>
+        <v>53.89971497203936</v>
       </c>
       <c r="AC77" t="n">
         <v>37.5386059595332</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.617260773068723</v>
+        <v>1.533497151382419</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.232259746331283</v>
+        <v>2.201868110367477</v>
       </c>
       <c r="AF77" t="n">
-        <v>0.947519646671782</v>
+        <v>0.9513453604352863</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.4736718860230856</v>
+        <v>0.4745601123012448</v>
       </c>
       <c r="AH77" t="n">
         <v>0.02238559531002598</v>
       </c>
       <c r="AI77" t="n">
-        <v>2.000371300536933</v>
+        <v>2.004688838726893</v>
       </c>
       <c r="AJ77" t="n">
-        <v>42.32720343369248</v>
+        <v>42.49810412721975</v>
       </c>
       <c r="AK77" t="n">
-        <v>79.74874857224916</v>
+        <v>79.98482311884563</v>
       </c>
       <c r="AL77" t="n">
-        <v>20.56772734175126</v>
+        <v>21.29536967128515</v>
       </c>
       <c r="AM77" t="n">
         <v>95.53530203501383</v>
       </c>
       <c r="AN77" t="n">
-        <v>3.877372898189094</v>
+        <v>3.75597251202912</v>
       </c>
       <c r="AO77" t="n">
-        <v>0.834756858182341</v>
+        <v>0.837227929520033</v>
       </c>
       <c r="AP77" t="n">
         <v>93.33333333333333</v>
       </c>
       <c r="AQ77" s="2" t="n">
-        <v>45374.56388888889</v>
+        <v>45374.56527777778</v>
       </c>
       <c r="AR77" s="2" t="n">
-        <v>45374.64236111111</v>
+        <v>45374.6375</v>
       </c>
       <c r="AS77" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45403.0625</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45402.04166666666</v>
+        <v>45402.04791666667</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>45402.47361111111</v>
@@ -12935,13 +12935,13 @@
         <v>1</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>45402.04166666666</v>
+        <v>45402.04791666667</v>
       </c>
       <c r="Q78" s="2" t="n">
         <v>45402.47361111111</v>
       </c>
       <c r="R78" t="n">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -12970,61 +12970,61 @@
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>67.13141679964865</v>
+        <v>67.17587077619133</v>
       </c>
       <c r="AB78" t="n">
-        <v>30.20530612723682</v>
+        <v>32.69347970987898</v>
       </c>
       <c r="AC78" t="n">
         <v>31.59116811690176</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.22250410298324</v>
+        <v>2.054717679864857</v>
       </c>
       <c r="AE78" t="n">
-        <v>2.125005841861615</v>
+        <v>2.126413006559615</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.2929361793446986</v>
+        <v>0.2899756310566987</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.4181076058558801</v>
+        <v>0.4148047825046337</v>
       </c>
       <c r="AH78" t="n">
         <v>0.03195305103814126</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.7006238950019781</v>
+        <v>0.6990653032151563</v>
       </c>
       <c r="AJ78" t="n">
-        <v>9.167706050825339</v>
+        <v>9.075052980404427</v>
       </c>
       <c r="AK78" t="n">
-        <v>23.96955747041144</v>
+        <v>23.89190155409921</v>
       </c>
       <c r="AL78" t="n">
-        <v>8.375594074154893</v>
+        <v>9.630072719479601</v>
       </c>
       <c r="AM78" t="n">
         <v>16.06150618394216</v>
       </c>
       <c r="AN78" t="n">
-        <v>2.861833710921574</v>
+        <v>2.480967927248456</v>
       </c>
       <c r="AO78" t="n">
-        <v>1.492360504419911</v>
+        <v>1.487525595699465</v>
       </c>
       <c r="AP78" t="n">
         <v>93.33333333333333</v>
       </c>
       <c r="AQ78" s="2" t="n">
-        <v>45402.04166666666</v>
+        <v>45402.04791666667</v>
       </c>
       <c r="AR78" s="2" t="n">
         <v>45402.47361111111</v>
       </c>
       <c r="AS78" t="n">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45421.93055555555</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45421.66597222222</v>
+        <v>45421.66805555556</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>45421.79722222222</v>
@@ -13096,13 +13096,13 @@
         <v>1</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>45421.66597222222</v>
+        <v>45421.66805555556</v>
       </c>
       <c r="Q79" s="2" t="n">
         <v>45421.79722222222</v>
       </c>
       <c r="R79" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -13131,49 +13131,49 @@
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>118.7152477425125</v>
+        <v>119.2550728299996</v>
       </c>
       <c r="AB79" t="n">
-        <v>20.60508605006301</v>
+        <v>22.31322433501115</v>
       </c>
       <c r="AC79" t="n">
         <v>25.28990759252019</v>
       </c>
       <c r="AD79" t="n">
-        <v>5.761453626258915</v>
+        <v>5.344591666336602</v>
       </c>
       <c r="AE79" t="n">
-        <v>4.694174832715641</v>
+        <v>4.715520307605663</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.594624232765293</v>
+        <v>1.602200592030091</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.9975612195938888</v>
+        <v>1.00361251174907</v>
       </c>
       <c r="AH79" t="n">
         <v>0.2088204870215321</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.598522678552472</v>
+        <v>1.596433457408594</v>
       </c>
       <c r="AJ79" t="n">
-        <v>7.636339975592848</v>
+        <v>7.67262166123041</v>
       </c>
       <c r="AK79" t="n">
-        <v>24.80198918629891</v>
+        <v>24.78554716345764</v>
       </c>
       <c r="AL79" t="n">
-        <v>5.216850025455157</v>
+        <v>5.798102870086828</v>
       </c>
       <c r="AM79" t="n">
         <v>2.373788599933808</v>
       </c>
       <c r="AN79" t="n">
-        <v>4.754207819906611</v>
+        <v>4.274768440437565</v>
       </c>
       <c r="AO79" t="n">
-        <v>10.44827209423388</v>
+        <v>10.44134560430056</v>
       </c>
       <c r="AP79" t="n">
         <v>100</v>
@@ -13234,7 +13234,7 @@
         <v>45434.41180555556</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45433.33958333333</v>
+        <v>45433.34861111111</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>45433.90694444445</v>
@@ -13257,13 +13257,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>45433.33958333333</v>
+        <v>45433.34861111111</v>
       </c>
       <c r="Q80" s="2" t="n">
         <v>45433.90694444445</v>
       </c>
       <c r="R80" t="n">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -13292,61 +13292,61 @@
         <v>2</v>
       </c>
       <c r="AA80" t="n">
-        <v>20.07647941348837</v>
+        <v>20.20423583776271</v>
       </c>
       <c r="AB80" t="n">
-        <v>5.55399831738737</v>
+        <v>6.339020580045969</v>
       </c>
       <c r="AC80" t="n">
         <v>9.271582375750192</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.614779527504872</v>
+        <v>3.187280366522519</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.165377882636126</v>
+        <v>2.179157237561395</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.467014851901852</v>
+        <v>2.437075246009265</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.440845959368919</v>
+        <v>0.8730992167909141</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.03888800876087165</v>
+        <v>0.03888800876086975</v>
       </c>
       <c r="AI80" t="n">
-        <v>5.596092692861332</v>
+        <v>2.791292443219411</v>
       </c>
       <c r="AJ80" t="n">
-        <v>63.43896050507255</v>
+        <v>62.66906750086728</v>
       </c>
       <c r="AK80" t="n">
-        <v>10.78892859509226</v>
+        <v>10.852818047183</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.542564221316328</v>
+        <v>3.154375329830994</v>
       </c>
       <c r="AM80" t="n">
         <v>3.238434804789722</v>
       </c>
       <c r="AN80" t="n">
-        <v>4.243325893065016</v>
+        <v>3.440560146583594</v>
       </c>
       <c r="AO80" t="n">
-        <v>3.331525642923298</v>
+        <v>3.3512541401579</v>
       </c>
       <c r="AP80" t="n">
-        <v>99.02080783353733</v>
+        <v>99.00497512437812</v>
       </c>
       <c r="AQ80" s="2" t="n">
-        <v>45433.33958333333</v>
+        <v>45433.34861111111</v>
       </c>
       <c r="AR80" s="2" t="n">
         <v>45433.90694444445</v>
       </c>
       <c r="AS80" t="n">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>45457.21527777778</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45457.00347222222</v>
+        <v>45457.00416666667</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>45457.07083333333</v>
@@ -13453,19 +13453,19 @@
         <v>1</v>
       </c>
       <c r="AA81" t="n">
-        <v>27.61083092377054</v>
+        <v>27.61083092377053</v>
       </c>
       <c r="AB81" t="n">
         <v>24.39586395021498</v>
       </c>
       <c r="AC81" t="n">
-        <v>29.91280321085896</v>
+        <v>29.91280321085895</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.131783280154226</v>
+        <v>1.131783280154225</v>
       </c>
       <c r="AE81" t="n">
-        <v>0.9230439129739352</v>
+        <v>0.923043912973935</v>
       </c>
       <c r="AF81" t="n">
         <v>0.3743217113851525</v>
@@ -13715,7 +13715,7 @@
         <v>45498.50416666667</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45497.725</v>
+        <v>45497.73055555556</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>45498.08333333334</v>
@@ -13738,13 +13738,13 @@
         <v>1</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>45497.725</v>
+        <v>45497.73055555556</v>
       </c>
       <c r="Q83" s="2" t="n">
         <v>45498.08333333334</v>
       </c>
       <c r="R83" t="n">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -13773,61 +13773,61 @@
         <v>2</v>
       </c>
       <c r="AA83" t="n">
-        <v>44.16172262515925</v>
+        <v>44.73575278239854</v>
       </c>
       <c r="AB83" t="n">
-        <v>8.413488401800029</v>
+        <v>8.221838625353062</v>
       </c>
       <c r="AC83" t="n">
         <v>15.33211056443664</v>
       </c>
       <c r="AD83" t="n">
-        <v>5.248919415603051</v>
+        <v>5.441088644631176</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.880342040292476</v>
+        <v>2.917781775339181</v>
       </c>
       <c r="AF83" t="n">
-        <v>2.136235023893521</v>
+        <v>2.157641953270424</v>
       </c>
       <c r="AG83" t="n">
-        <v>1.065103425733988</v>
+        <v>1.038145908174227</v>
       </c>
       <c r="AH83" t="n">
         <v>0.02088248399788313</v>
       </c>
       <c r="AI83" t="n">
-        <v>2.005659706165522</v>
+        <v>2.078360985947572</v>
       </c>
       <c r="AJ83" t="n">
-        <v>102.2979365917423</v>
+        <v>103.323050719883</v>
       </c>
       <c r="AK83" t="n">
-        <v>17.50093067443186</v>
+        <v>17.73593378853141</v>
       </c>
       <c r="AL83" t="n">
-        <v>2.58122845304509</v>
+        <v>2.440971526627739</v>
       </c>
       <c r="AM83" t="n">
         <v>5.307186279601107</v>
       </c>
       <c r="AN83" t="n">
-        <v>6.780078165412252</v>
+        <v>7.265932271251859</v>
       </c>
       <c r="AO83" t="n">
-        <v>3.297591181545496</v>
+        <v>3.341871352189367</v>
       </c>
       <c r="AP83" t="n">
         <v>100</v>
       </c>
       <c r="AQ83" s="2" t="n">
-        <v>45497.725</v>
+        <v>45497.73055555556</v>
       </c>
       <c r="AR83" s="2" t="n">
         <v>45498.08333333334</v>
       </c>
       <c r="AS83" t="n">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45500.43611111111</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45499.86041666667</v>
+        <v>45499.86597222222</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>45500.19305555556</v>
@@ -13934,7 +13934,7 @@
         <v>1</v>
       </c>
       <c r="AA84" t="n">
-        <v>5.613060599853961</v>
+        <v>5.613060599853976</v>
       </c>
       <c r="AB84" t="n">
         <v>9.074017459937087</v>
@@ -13943,10 +13943,10 @@
         <v>9.689695753859874</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.6185860479810977</v>
+        <v>0.6185860479810994</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.5792814080481328</v>
+        <v>0.5792814080481343</v>
       </c>
       <c r="AF84" t="n">
         <v>0.6074964869081343</v>
@@ -14196,7 +14196,7 @@
         <v>45502.31041666667</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45501.98055555556</v>
+        <v>45501.98263888889</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>45502.11041666667</v>
@@ -14257,16 +14257,16 @@
         <v>8.294430317650161</v>
       </c>
       <c r="AB86" t="n">
-        <v>7.576408541135577</v>
+        <v>7.576408541135578</v>
       </c>
       <c r="AC86" t="n">
-        <v>7.737622472791023</v>
+        <v>7.737622472791018</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.094770731094573</v>
+        <v>1.094770731094572</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.071961102627729</v>
+        <v>1.07196110262773</v>
       </c>
       <c r="AF86" t="n">
         <v>1.412948103828273</v>
@@ -14516,7 +14516,7 @@
         <v>45515.64513888889</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45515.42291666667</v>
+        <v>45515.425</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>45515.53055555555</v>
@@ -14577,7 +14577,7 @@
         <v>8.666596903756806</v>
       </c>
       <c r="AB88" t="n">
-        <v>7.993369659937183</v>
+        <v>7.993369659937182</v>
       </c>
       <c r="AC88" t="n">
         <v>10.62563107415726</v>
@@ -14592,16 +14592,16 @@
         <v>0.1055662507358139</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.09822552431001257</v>
+        <v>0.09822552431001251</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.1937964125125232</v>
+        <v>0.1937964125125233</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.074733390097598</v>
+        <v>1.074733390097599</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.5447275796655529</v>
+        <v>0.5447275796655527</v>
       </c>
       <c r="AK88" t="n">
         <v>4.173990921676159</v>
@@ -14677,7 +14677,7 @@
         <v>45531.3125</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45530.34305555555</v>
+        <v>45530.34930555556</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>45530.76527777778</v>
@@ -14738,31 +14738,31 @@
         <v>31.71615147586229</v>
       </c>
       <c r="AB89" t="n">
-        <v>38.13445759493636</v>
+        <v>38.13445759493632</v>
       </c>
       <c r="AC89" t="n">
-        <v>26.33880111847393</v>
+        <v>26.33880111847402</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.8316927386971326</v>
+        <v>0.8316927386971336</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.204160786711614</v>
+        <v>1.204160786711609</v>
       </c>
       <c r="AF89" t="n">
-        <v>0.233815777257236</v>
+        <v>0.2338157772572359</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.4218342131254789</v>
+        <v>0.4218342131254788</v>
       </c>
       <c r="AH89" t="n">
         <v>0.1263543351457739</v>
       </c>
       <c r="AI89" t="n">
-        <v>0.5542835786714273</v>
+        <v>0.5542835786714272</v>
       </c>
       <c r="AJ89" t="n">
-        <v>1.850476890939157</v>
+        <v>1.850476890939156</v>
       </c>
       <c r="AK89" t="n">
         <v>7.786245355018764</v>
@@ -14838,7 +14838,7 @@
         <v>45539.78333333333</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45539.58125</v>
+        <v>45539.58333333334</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>45539.69513888889</v>
@@ -15158,7 +15158,7 @@
         <v>45540.99583333333</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45540.94791666666</v>
+        <v>45540.94861111111</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>45540.96388888889</v>
@@ -15181,13 +15181,13 @@
         <v>1</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>45540.94791666666</v>
+        <v>45540.94861111111</v>
       </c>
       <c r="Q92" s="2" t="n">
         <v>45540.95208333333</v>
       </c>
       <c r="R92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S92" t="n">
         <v>6</v>
@@ -15216,61 +15216,61 @@
         <v>1</v>
       </c>
       <c r="AA92" t="n">
-        <v>103.032500596694</v>
+        <v>103.2681616747821</v>
       </c>
       <c r="AB92" t="n">
-        <v>50.69650423052872</v>
+        <v>51.22684717440312</v>
       </c>
       <c r="AC92" t="n">
-        <v>18.58782868666643</v>
+        <v>18.58782868666642</v>
       </c>
       <c r="AD92" t="n">
-        <v>2.032339352792086</v>
+        <v>2.015899228059126</v>
       </c>
       <c r="AE92" t="n">
-        <v>5.54300894060865</v>
+        <v>5.555687187329163</v>
       </c>
       <c r="AF92" t="n">
-        <v>0.5468526044105578</v>
+        <v>0.5263265165248328</v>
       </c>
       <c r="AG92" t="n">
-        <v>0.8398665186279012</v>
+        <v>0.8428904634749408</v>
       </c>
       <c r="AH92" t="n">
         <v>0.1788387494981265</v>
       </c>
       <c r="AI92" t="n">
-        <v>0.6511184721400214</v>
+        <v>0.6244305035258956</v>
       </c>
       <c r="AJ92" t="n">
-        <v>3.057797071077633</v>
+        <v>2.943022795685263</v>
       </c>
       <c r="AK92" t="n">
-        <v>38.20629278818766</v>
+        <v>38.6534008026123</v>
       </c>
       <c r="AL92" t="n">
-        <v>7.61704603433609</v>
+        <v>7.757029847304026</v>
       </c>
       <c r="AM92" t="n">
         <v>27.08926466405392</v>
       </c>
       <c r="AN92" t="n">
-        <v>5.015893643803843</v>
+        <v>4.983015608228758</v>
       </c>
       <c r="AO92" t="n">
-        <v>1.410385009043286</v>
+        <v>1.426889998011035</v>
       </c>
       <c r="AP92" t="n">
         <v>100</v>
       </c>
       <c r="AQ92" s="2" t="n">
-        <v>45540.94791666666</v>
+        <v>45540.94861111111</v>
       </c>
       <c r="AR92" s="2" t="n">
         <v>45540.95208333333</v>
       </c>
       <c r="AS92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45541.82986111111</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45541.05555555555</v>
+        <v>45541.05833333333</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>45541.31875</v>
@@ -15342,13 +15342,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>45541.05555555555</v>
+        <v>45541.05833333333</v>
       </c>
       <c r="Q93" s="2" t="n">
         <v>45541.31875</v>
       </c>
       <c r="R93" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -15377,49 +15377,49 @@
         <v>1</v>
       </c>
       <c r="AA93" t="n">
-        <v>30.03500372118397</v>
+        <v>29.95043654011621</v>
       </c>
       <c r="AB93" t="n">
-        <v>13.78098735446409</v>
+        <v>14.39729140869491</v>
       </c>
       <c r="AC93" t="n">
         <v>7.144272201265434</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.179452237248785</v>
+        <v>2.080282720542028</v>
       </c>
       <c r="AE93" t="n">
-        <v>4.204067660784818</v>
+        <v>4.192230600453776</v>
       </c>
       <c r="AF93" t="n">
-        <v>0.2361850754425874</v>
+        <v>0.2361377948166756</v>
       </c>
       <c r="AG93" t="n">
-        <v>0.1857896298114081</v>
+        <v>0.190081751327151</v>
       </c>
       <c r="AH93" t="n">
         <v>0.00708185117390426</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.27125004599199</v>
+        <v>1.242295976167945</v>
       </c>
       <c r="AJ93" t="n">
-        <v>33.35075386968029</v>
+        <v>33.34407756079568</v>
       </c>
       <c r="AK93" t="n">
-        <v>32.12235582488685</v>
+        <v>31.99629702139397</v>
       </c>
       <c r="AL93" t="n">
-        <v>23.58098184516033</v>
+        <v>24.22492873122295</v>
       </c>
       <c r="AM93" t="n">
         <v>23.52288162708282</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.362214518284764</v>
+        <v>1.320800460401549</v>
       </c>
       <c r="AO93" t="n">
-        <v>1.36557911288824</v>
+        <v>1.360220126455739</v>
       </c>
       <c r="AP93" t="n">
         <v>100</v>
@@ -15480,7 +15480,7 @@
         <v>45543.11597222222</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45542.47291666667</v>
+        <v>45542.47708333333</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>45542.74236111111</v>
@@ -15503,13 +15503,13 @@
         <v>1</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>45542.47291666667</v>
+        <v>45542.47777777778</v>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>45542.72152777778</v>
+        <v>45542.72291666667</v>
       </c>
       <c r="R94" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -15518,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -15538,52 +15538,52 @@
         <v>1</v>
       </c>
       <c r="AA94" t="n">
-        <v>3.093772232499871</v>
+        <v>3.116438563509115</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.860782373796827</v>
+        <v>1.858186166369253</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.387577907222751</v>
+        <v>1.398386638249605</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.662619055331653</v>
+        <v>1.677140116481647</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.229620561408392</v>
+        <v>2.228595781929123</v>
       </c>
       <c r="AF94" t="n">
-        <v>0.1292635199179525</v>
+        <v>0.1308731453868994</v>
       </c>
       <c r="AG94" t="n">
-        <v>0.03371854185992058</v>
+        <v>0.03373279581625134</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.06433468286534794</v>
+        <v>0.06542259194513142</v>
       </c>
       <c r="AI94" t="n">
-        <v>3.833603494924587</v>
+        <v>3.879700517555353</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2.009235363582971</v>
+        <v>2.000427398178598</v>
       </c>
       <c r="AK94" t="n">
-        <v>8.426728785246111</v>
+        <v>8.418550292636787</v>
       </c>
       <c r="AL94" t="n">
-        <v>3.690958344750106</v>
+        <v>3.941493971956273</v>
       </c>
       <c r="AM94" t="n">
-        <v>9.096561119953792</v>
+        <v>9.115623027086258</v>
       </c>
       <c r="AN94" t="n">
-        <v>2.283073391286575</v>
+        <v>2.135878007814998</v>
       </c>
       <c r="AO94" t="n">
-        <v>0.9263642242519133</v>
+        <v>0.9235298857381244</v>
       </c>
       <c r="AP94" t="n">
-        <v>97.76536312849163</v>
+        <v>97.73371104815864</v>
       </c>
       <c r="AQ94" s="2" t="n">
         <v>45542.51180555556</v>
@@ -15641,7 +15641,7 @@
         <v>45545.52222222222</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45545.16319444445</v>
+        <v>45545.16666666666</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>45545.34652777778</v>
@@ -15664,13 +15664,13 @@
         <v>1</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>45545.16319444445</v>
+        <v>45545.16666666666</v>
       </c>
       <c r="Q95" s="2" t="n">
         <v>45545.34652777778</v>
       </c>
       <c r="R95" t="n">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -15699,61 +15699,61 @@
         <v>1</v>
       </c>
       <c r="AA95" t="n">
-        <v>70.43692619950419</v>
+        <v>70.12148441193055</v>
       </c>
       <c r="AB95" t="n">
-        <v>26.71495764326166</v>
+        <v>29.42917630484074</v>
       </c>
       <c r="AC95" t="n">
         <v>35.99623069532751</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.636610064671788</v>
+        <v>2.382719913244613</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.956786164520477</v>
+        <v>1.948022975112021</v>
       </c>
       <c r="AF95" t="n">
-        <v>0.8261832667573665</v>
+        <v>0.8232730097185721</v>
       </c>
       <c r="AG95" t="n">
-        <v>0.3575390028608379</v>
+        <v>0.3862457948727375</v>
       </c>
       <c r="AH95" t="n">
         <v>0.3017843329180664</v>
       </c>
       <c r="AI95" t="n">
-        <v>2.310750044461402</v>
+        <v>2.13147436333858</v>
       </c>
       <c r="AJ95" t="n">
-        <v>2.737661225712711</v>
+        <v>2.728017726294918</v>
       </c>
       <c r="AK95" t="n">
-        <v>25.13214611469514</v>
+        <v>24.9489161977868</v>
       </c>
       <c r="AL95" t="n">
-        <v>13.41117632153134</v>
+        <v>14.12470663152635</v>
       </c>
       <c r="AM95" t="n">
         <v>16.80360807279746</v>
       </c>
       <c r="AN95" t="n">
-        <v>1.873970300006127</v>
+        <v>1.766331637791387</v>
       </c>
       <c r="AO95" t="n">
-        <v>1.495639865308472</v>
+        <v>1.484735664489544</v>
       </c>
       <c r="AP95" t="n">
         <v>100</v>
       </c>
       <c r="AQ95" s="2" t="n">
-        <v>45545.16388888889</v>
+        <v>45545.16666666666</v>
       </c>
       <c r="AR95" s="2" t="n">
-        <v>45545.33402777778</v>
+        <v>45545.32986111111</v>
       </c>
       <c r="AS95" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45547.375</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45546.63194444445</v>
+        <v>45546.63402777778</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>45546.83888888889</v>
@@ -15878,16 +15878,16 @@
         <v>0.1505020223532378</v>
       </c>
       <c r="AG96" t="n">
-        <v>0.3578836449055201</v>
+        <v>0.3578836449055202</v>
       </c>
       <c r="AH96" t="n">
-        <v>0.3766608666927687</v>
+        <v>0.3766608666927689</v>
       </c>
       <c r="AI96" t="n">
-        <v>0.4205333898199505</v>
+        <v>0.4205333898199504</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0.3995690438316703</v>
+        <v>0.39956904383167</v>
       </c>
       <c r="AK96" t="n">
         <v>8.046809061753507</v>
@@ -15963,7 +15963,7 @@
         <v>45566.12361111111</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45565.85833333333</v>
+        <v>45565.86041666667</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>45565.98541666667</v>
@@ -15986,13 +15986,13 @@
         <v>1</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>45565.85833333333</v>
+        <v>45565.86111111111</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>45565.95208333333</v>
+        <v>45565.95277777778</v>
       </c>
       <c r="R97" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -16001,7 +16001,7 @@
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -16021,61 +16021,61 @@
         <v>1</v>
       </c>
       <c r="AA97" t="n">
-        <v>93.93549653774093</v>
+        <v>94.5743719443461</v>
       </c>
       <c r="AB97" t="n">
-        <v>71.72268419183332</v>
+        <v>70.32166106035682</v>
       </c>
       <c r="AC97" t="n">
-        <v>102.6761665885362</v>
+        <v>102.3989311928927</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.309704141670103</v>
+        <v>1.344882508721932</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.9148714804885284</v>
+        <v>0.9235874910275459</v>
       </c>
       <c r="AF97" t="n">
-        <v>0.2638656590847295</v>
+        <v>0.2646073774302102</v>
       </c>
       <c r="AG97" t="n">
-        <v>0.1196537130564374</v>
+        <v>0.1229409790782539</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.1316766479861482</v>
+        <v>0.1321367244401036</v>
       </c>
       <c r="AI97" t="n">
-        <v>2.205244219711521</v>
+        <v>2.152312267350525</v>
       </c>
       <c r="AJ97" t="n">
-        <v>2.003891070438602</v>
+        <v>2.002527144148744</v>
       </c>
       <c r="AK97" t="n">
-        <v>25.94203576953323</v>
+        <v>25.97287969426675</v>
       </c>
       <c r="AL97" t="n">
-        <v>5.423110100844254</v>
+        <v>5.962659366149455</v>
       </c>
       <c r="AM97" t="n">
-        <v>41.02673383454482</v>
+        <v>41.24036624332269</v>
       </c>
       <c r="AN97" t="n">
-        <v>4.783608535901686</v>
+        <v>4.355922097733284</v>
       </c>
       <c r="AO97" t="n">
-        <v>0.6323202786298781</v>
+        <v>0.6297926536593761</v>
       </c>
       <c r="AP97" t="n">
         <v>100</v>
       </c>
       <c r="AQ97" s="2" t="n">
-        <v>45565.85833333333</v>
+        <v>45565.86111111111</v>
       </c>
       <c r="AR97" s="2" t="n">
-        <v>45565.95208333333</v>
+        <v>45565.95277777778</v>
       </c>
       <c r="AS97" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45569.26875</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45569.18055555555</v>
+        <v>45569.18194444444</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>45569.23888888889</v>
@@ -16203,13 +16203,13 @@
         <v>0.5776072490643107</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.6205930146481674</v>
+        <v>0.6205930146481676</v>
       </c>
       <c r="AI98" t="n">
         <v>0.799019184317079</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.7436746178405608</v>
+        <v>0.7436746178405605</v>
       </c>
       <c r="AK98" t="n">
         <v>16.54708271026611</v>
@@ -16285,7 +16285,7 @@
         <v>45574.71597222222</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45574.63055555556</v>
+        <v>45574.63194444445</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>45574.67777777778</v>
@@ -16358,19 +16358,19 @@
         <v>1.358028439631342</v>
       </c>
       <c r="AF99" t="n">
-        <v>0.9511548650111794</v>
+        <v>0.9511548650111779</v>
       </c>
       <c r="AG99" t="n">
-        <v>0.4652916282826057</v>
+        <v>0.4652916282826058</v>
       </c>
       <c r="AH99" t="n">
         <v>0.4309741878677838</v>
       </c>
       <c r="AI99" t="n">
-        <v>2.044212290089761</v>
+        <v>2.044212290089758</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.206988009460508</v>
+        <v>2.206988009460505</v>
       </c>
       <c r="AK99" t="n">
         <v>46.99563102258576</v>
@@ -16446,7 +16446,7 @@
         <v>45578.07222222222</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>45577.93888888889</v>
+        <v>45577.94027777778</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>45578.0125</v>
@@ -16504,7 +16504,7 @@
         <v>1</v>
       </c>
       <c r="AA100" t="n">
-        <v>80.61849057984008</v>
+        <v>80.61849057984013</v>
       </c>
       <c r="AB100" t="n">
         <v>82.23595991617371</v>
@@ -16513,10 +16513,10 @@
         <v>103.5714640839895</v>
       </c>
       <c r="AD100" t="n">
-        <v>0.9803313618764543</v>
+        <v>0.9803313618764549</v>
       </c>
       <c r="AE100" t="n">
-        <v>0.7783851593954868</v>
+        <v>0.7783851593954871</v>
       </c>
       <c r="AF100" t="n">
         <v>0.1714036874438923</v>
@@ -16607,7 +16607,7 @@
         <v>45578.33472222222</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>45578.08680555555</v>
+        <v>45578.08888888889</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>45578.19652777778</v>
@@ -16671,13 +16671,13 @@
         <v>147.5967199022976</v>
       </c>
       <c r="AC101" t="n">
-        <v>124.2903245040516</v>
+        <v>124.2903245040517</v>
       </c>
       <c r="AD101" t="n">
         <v>2.002871283582853</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.378441226402117</v>
+        <v>2.378441226402116</v>
       </c>
       <c r="AF101" t="n">
         <v>0.5076797851141421</v>
@@ -16768,7 +16768,7 @@
         <v>45579.22013888889</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>45578.71944444445</v>
+        <v>45578.72222222222</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>45578.90902777778</v>
@@ -16832,25 +16832,25 @@
         <v>182.1317053578219</v>
       </c>
       <c r="AC102" t="n">
-        <v>148.9166967678069</v>
+        <v>148.9166967678072</v>
       </c>
       <c r="AD102" t="n">
         <v>1.350478882751693</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.651695392819545</v>
+        <v>1.651695392819542</v>
       </c>
       <c r="AF102" t="n">
         <v>0.2750715124796281</v>
       </c>
       <c r="AG102" t="n">
-        <v>0.3079595194098964</v>
+        <v>0.3079595194098969</v>
       </c>
       <c r="AH102" t="n">
         <v>0.08774185075658446</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.8932067208271809</v>
+        <v>0.8932067208271796</v>
       </c>
       <c r="AJ102" t="n">
         <v>3.135009235703702</v>
@@ -17247,7 +17247,7 @@
         <v>45658.26111111111</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>45657.75416666667</v>
+        <v>45657.75833333333</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>45658.00486111111</v>
@@ -17270,13 +17270,13 @@
         <v>1</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>45657.75416666667</v>
+        <v>45657.75833333333</v>
       </c>
       <c r="Q105" s="2" t="n">
         <v>45658.00486111111</v>
       </c>
       <c r="R105" t="n">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -17305,61 +17305,61 @@
         <v>2</v>
       </c>
       <c r="AA105" t="n">
-        <v>52.0479748423293</v>
+        <v>52.03281248822263</v>
       </c>
       <c r="AB105" t="n">
-        <v>22.11765485114521</v>
+        <v>23.38991725990802</v>
       </c>
       <c r="AC105" t="n">
         <v>22.5572356644826</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.353232076032435</v>
+        <v>2.22458300771378</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.307373811955213</v>
+        <v>2.306701639427861</v>
       </c>
       <c r="AF105" t="n">
-        <v>2.030163224759378</v>
+        <v>2.059231407936638</v>
       </c>
       <c r="AG105" t="n">
-        <v>0.559070966928876</v>
+        <v>0.4568657050886706</v>
       </c>
       <c r="AH105" t="n">
         <v>0.1150007951775147</v>
       </c>
       <c r="AI105" t="n">
-        <v>3.631315780734597</v>
+        <v>4.507301346983295</v>
       </c>
       <c r="AJ105" t="n">
-        <v>17.6534711923133</v>
+        <v>17.90623625478431</v>
       </c>
       <c r="AK105" t="n">
-        <v>9.291672764057061</v>
+        <v>9.167917221359593</v>
       </c>
       <c r="AL105" t="n">
-        <v>6.908297615001599</v>
+        <v>7.355992890149355</v>
       </c>
       <c r="AM105" t="n">
         <v>6.207740876078605</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.345001805347801</v>
+        <v>1.246319478317692</v>
       </c>
       <c r="AO105" t="n">
-        <v>1.496788114958587</v>
+        <v>1.47685243381984</v>
       </c>
       <c r="AP105" t="n">
         <v>100</v>
       </c>
       <c r="AQ105" s="2" t="n">
-        <v>45657.75416666667</v>
+        <v>45657.75833333333</v>
       </c>
       <c r="AR105" s="2" t="n">
         <v>45658.00486111111</v>
       </c>
       <c r="AS105" t="n">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45658.41041666667</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>45658.24305555555</v>
+        <v>45658.24375</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>45658.29166666666</v>
@@ -17472,7 +17472,7 @@
         <v>28.59368236315892</v>
       </c>
       <c r="AC106" t="n">
-        <v>47.54170839159394</v>
+        <v>47.54170839159395</v>
       </c>
       <c r="AD106" t="n">
         <v>1.962173004748805</v>
@@ -17481,7 +17481,7 @@
         <v>1.180137473757101</v>
       </c>
       <c r="AF106" t="n">
-        <v>0.4167555774332261</v>
+        <v>0.4167555774332262</v>
       </c>
       <c r="AG106" t="n">
         <v>0.1932604783843543</v>
@@ -17490,10 +17490,10 @@
         <v>0.2311763792463206</v>
       </c>
       <c r="AI106" t="n">
-        <v>2.156444923024495</v>
+        <v>2.156444923024496</v>
       </c>
       <c r="AJ106" t="n">
-        <v>1.802760207560691</v>
+        <v>1.802760207560692</v>
       </c>
       <c r="AK106" t="n">
         <v>5.260393634438515</v>
@@ -18046,7 +18046,7 @@
         <v>45684.46805555555</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>45684.28680555556</v>
+        <v>45684.2875</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>45684.34583333333</v>
@@ -18104,34 +18104,34 @@
         <v>1</v>
       </c>
       <c r="AA110" t="n">
-        <v>21.11887317038991</v>
+        <v>21.11887317038992</v>
       </c>
       <c r="AB110" t="n">
-        <v>25.48157696706275</v>
+        <v>25.48157696706276</v>
       </c>
       <c r="AC110" t="n">
         <v>19.95101533646933</v>
       </c>
       <c r="AD110" t="n">
-        <v>0.8287898821053331</v>
+        <v>0.8287898821053334</v>
       </c>
       <c r="AE110" t="n">
         <v>1.058536260647638</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.213681441568924</v>
+        <v>1.213681441568925</v>
       </c>
       <c r="AG110" t="n">
-        <v>2.459629966925796</v>
+        <v>2.459629966925795</v>
       </c>
       <c r="AH110" t="n">
         <v>0.7109799831916822</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.4934406629814568</v>
+        <v>0.4934406629814574</v>
       </c>
       <c r="AJ110" t="n">
-        <v>1.707054305693036</v>
+        <v>1.707054305693038</v>
       </c>
       <c r="AK110" t="n">
         <v>1.595277817577732</v>
@@ -18207,7 +18207,7 @@
         <v>45691.16666666666</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>45689.75347222222</v>
+        <v>45689.75902777778</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>45690.24027777778</v>
@@ -18230,13 +18230,13 @@
         <v>1</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>45689.75347222222</v>
+        <v>45689.75902777778</v>
       </c>
       <c r="Q111" s="2" t="n">
         <v>45690.24027777778</v>
       </c>
       <c r="R111" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -18265,61 +18265,61 @@
         <v>2</v>
       </c>
       <c r="AA111" t="n">
-        <v>23.10324063950949</v>
+        <v>23.05412302486247</v>
       </c>
       <c r="AB111" t="n">
-        <v>8.282990047681478</v>
+        <v>9.619528970688949</v>
       </c>
       <c r="AC111" t="n">
         <v>5.984902109533111</v>
       </c>
       <c r="AD111" t="n">
-        <v>2.789239212713579</v>
+        <v>2.396595830742775</v>
       </c>
       <c r="AE111" t="n">
-        <v>3.860253721227832</v>
+        <v>3.852046800922689</v>
       </c>
       <c r="AF111" t="n">
-        <v>2.048705706943463</v>
+        <v>2.067069678808728</v>
       </c>
       <c r="AG111" t="n">
-        <v>0.7136051891662596</v>
+        <v>0.7054164789791947</v>
       </c>
       <c r="AH111" t="n">
         <v>0.04230884453478628</v>
       </c>
       <c r="AI111" t="n">
-        <v>2.870923219234248</v>
+        <v>2.930282663370689</v>
       </c>
       <c r="AJ111" t="n">
-        <v>48.42263430898047</v>
+        <v>48.85668000479631</v>
       </c>
       <c r="AK111" t="n">
-        <v>10.49535082403395</v>
+        <v>10.46427188800247</v>
       </c>
       <c r="AL111" t="n">
-        <v>3.60267262707154</v>
+        <v>4.41494651529938</v>
       </c>
       <c r="AM111" t="n">
         <v>8.325895104805628</v>
       </c>
       <c r="AN111" t="n">
-        <v>2.91321247042232</v>
+        <v>2.370192221296453</v>
       </c>
       <c r="AO111" t="n">
-        <v>1.260567265371399</v>
+        <v>1.256834461193559</v>
       </c>
       <c r="AP111" t="n">
         <v>100</v>
       </c>
       <c r="AQ111" s="2" t="n">
-        <v>45689.75347222222</v>
+        <v>45689.75902777778</v>
       </c>
       <c r="AR111" s="2" t="n">
         <v>45690.24027777778</v>
       </c>
       <c r="AS111" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45708.91041666667</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>45708.54652777778</v>
+        <v>45708.54722222222</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>45708.64097222222</v>
@@ -18426,7 +18426,7 @@
         <v>1</v>
       </c>
       <c r="AA112" t="n">
-        <v>30.29715736962427</v>
+        <v>30.29715736962428</v>
       </c>
       <c r="AB112" t="n">
         <v>34.9425025491476</v>
@@ -18435,22 +18435,22 @@
         <v>44.55291726823387</v>
       </c>
       <c r="AD112" t="n">
-        <v>0.8670574560883406</v>
+        <v>0.8670574560883409</v>
       </c>
       <c r="AE112" t="n">
-        <v>0.6800263423204854</v>
+        <v>0.6800263423204856</v>
       </c>
       <c r="AF112" t="n">
         <v>0.2914041599793742</v>
       </c>
       <c r="AG112" t="n">
-        <v>1.206573624015317</v>
+        <v>1.206573624015316</v>
       </c>
       <c r="AH112" t="n">
         <v>0.2634883472096424</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.2415137826481072</v>
+        <v>0.2415137826481073</v>
       </c>
       <c r="AJ112" t="n">
         <v>1.105947048760835</v>
@@ -18529,7 +18529,7 @@
         <v>45710.07291666666</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>45709.89583333334</v>
+        <v>45709.89722222222</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>45709.97013888889</v>
@@ -18593,25 +18593,25 @@
         <v>51.32896392564224</v>
       </c>
       <c r="AC113" t="n">
-        <v>53.25893685473689</v>
+        <v>53.2589368547369</v>
       </c>
       <c r="AD113" t="n">
         <v>1.006093428516761</v>
       </c>
       <c r="AE113" t="n">
-        <v>0.9696350762504843</v>
+        <v>0.9696350762504842</v>
       </c>
       <c r="AF113" t="n">
         <v>0.3272456206651171</v>
       </c>
       <c r="AG113" t="n">
-        <v>0.1977970728085706</v>
+        <v>0.1977970728085707</v>
       </c>
       <c r="AH113" t="n">
         <v>0.1592630910559203</v>
       </c>
       <c r="AI113" t="n">
-        <v>1.6544512819046</v>
+        <v>1.654451281904599</v>
       </c>
       <c r="AJ113" t="n">
         <v>2.054748645750037</v>
@@ -18690,7 +18690,7 @@
         <v>45710.74513888889</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>45710.28958333333</v>
+        <v>45710.29166666666</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>45710.45069444444</v>
@@ -18763,7 +18763,7 @@
         <v>2.052891973590081</v>
       </c>
       <c r="AF114" t="n">
-        <v>0.7692043367986683</v>
+        <v>0.7692043367986687</v>
       </c>
       <c r="AG114" t="n">
         <v>0.4150967277015427</v>
@@ -18772,10 +18772,10 @@
         <v>0.2141143221114946</v>
       </c>
       <c r="AI114" t="n">
-        <v>1.853072514105029</v>
+        <v>1.85307251410503</v>
       </c>
       <c r="AJ114" t="n">
-        <v>3.592493623094137</v>
+        <v>3.592493623094139</v>
       </c>
       <c r="AK114" t="n">
         <v>10.45881713554263</v>
@@ -18851,7 +18851,7 @@
         <v>45712.13402777778</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>45711.21805555555</v>
+        <v>45711.225</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>45711.65763888889</v>
@@ -19012,7 +19012,7 @@
         <v>45720.08888888889</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>45719.56388888889</v>
+        <v>45719.56875</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>45719.84375</v>
@@ -19073,13 +19073,13 @@
         <v>56.27391633781951</v>
       </c>
       <c r="AB116" t="n">
-        <v>63.53952261287726</v>
+        <v>63.53952261287727</v>
       </c>
       <c r="AC116" t="n">
         <v>39.29575258819053</v>
       </c>
       <c r="AD116" t="n">
-        <v>0.8856521740126317</v>
+        <v>0.8856521740126315</v>
       </c>
       <c r="AE116" t="n">
         <v>1.432061040478237</v>
@@ -19088,13 +19088,13 @@
         <v>0.4883753861138487</v>
       </c>
       <c r="AG116" t="n">
-        <v>0.858012377632711</v>
+        <v>0.8580123776327107</v>
       </c>
       <c r="AH116" t="n">
         <v>0.380461988859819</v>
       </c>
       <c r="AI116" t="n">
-        <v>0.5691938704442645</v>
+        <v>0.5691938704442647</v>
       </c>
       <c r="AJ116" t="n">
         <v>1.283637788829912</v>
@@ -19173,7 +19173,7 @@
         <v>45771.75069444445</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>45770.98125</v>
+        <v>45770.98541666667</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>45771.28402777778</v>
@@ -19234,13 +19234,13 @@
         <v>17.34523304872407</v>
       </c>
       <c r="AB117" t="n">
-        <v>35.6276041873496</v>
+        <v>35.62760418734959</v>
       </c>
       <c r="AC117" t="n">
         <v>19.90922711223734</v>
       </c>
       <c r="AD117" t="n">
-        <v>0.4868481461036016</v>
+        <v>0.4868481461036017</v>
       </c>
       <c r="AE117" t="n">
         <v>0.8712157910973201</v>
@@ -19249,13 +19249,13 @@
         <v>0.2393336896165839</v>
       </c>
       <c r="AG117" t="n">
-        <v>0.1193750733560069</v>
+        <v>0.119375073356007</v>
       </c>
       <c r="AH117" t="n">
         <v>0.08835269691729077</v>
       </c>
       <c r="AI117" t="n">
-        <v>2.004888314521322</v>
+        <v>2.00488831452132</v>
       </c>
       <c r="AJ117" t="n">
         <v>2.708844188883451</v>
@@ -19913,7 +19913,7 @@
         <v>44734.73680555556</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>44734.12777777778</v>
+        <v>44734.12847222222</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>44734.26458333333</v>
@@ -20006,7 +20006,7 @@
         <v>45049.67083333333</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45049.43333333333</v>
+        <v>45049.43402777778</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>45049.48611111111</v>
@@ -20099,7 +20099,7 @@
         <v>45121.09375</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45120.73125</v>
+        <v>45120.73194444444</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>45120.80625</v>
@@ -20192,7 +20192,7 @@
         <v>45271.69444444445</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45270.88541666666</v>
+        <v>45270.89444444444</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>45271.38888888889</v>
@@ -20285,7 +20285,7 @@
         <v>45540.94722222222</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45540.82569444444</v>
+        <v>45540.82638888889</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>45540.87083333333</v>
@@ -20378,7 +20378,7 @@
         <v>45541.05069444444</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45540.99652777778</v>
+        <v>45540.99722222222</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>45541.01736111111</v>
@@ -20471,7 +20471,7 @@
         <v>45603.47986111111</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45603.15416666667</v>
+        <v>45603.15625</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>45603.27638888889</v>
@@ -20746,7 +20746,7 @@
         <v>45608.50694444445</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45608.17708333334</v>
+        <v>45608.17777777778</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>45608.25763888889</v>
@@ -21100,7 +21100,7 @@
         <v>43941.38541666666</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>43940.2125</v>
+        <v>43940.21597222222</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>43940.57638888889</v>
@@ -21292,7 +21292,7 @@
         <v>44038.97986111111</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>44037.96597222222</v>
+        <v>44037.97222222222</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>44038.39513888889</v>
@@ -21389,7 +21389,7 @@
         <v>44066.10833333333</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>44064.80347222222</v>
+        <v>44064.81388888889</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>44065.475</v>
@@ -21486,7 +21486,7 @@
         <v>44148.76944444444</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>44147.97708333333</v>
+        <v>44147.98611111111</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>44148.47222222222</v>
@@ -21583,7 +21583,7 @@
         <v>44186.1875</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44184.86041666667</v>
+        <v>44184.87222222222</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>44185.57916666667</v>
@@ -21965,7 +21965,7 @@
         <v>44303.48263888889</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>44301.84791666667</v>
+        <v>44301.85972222222</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>44302.62361111111</v>
@@ -22157,7 +22157,7 @@
         <v>44379.15486111111</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>44377.95347222222</v>
+        <v>44377.96388888889</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>44378.60416666666</v>
@@ -22345,7 +22345,7 @@
         <v>44473.54097222222</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>44473.02152777778</v>
+        <v>44473.02708333333</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>44473.34166666667</v>
@@ -22438,7 +22438,7 @@
         <v>44593.94305555556</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44593.51527777778</v>
+        <v>44593.51736111111</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>44593.67777777778</v>
@@ -22535,7 +22535,7 @@
         <v>44669.35763888889</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44668.64791666667</v>
+        <v>44668.65</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>44668.87152777778</v>
@@ -22917,7 +22917,7 @@
         <v>45064.29791666667</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45064.21805555555</v>
+        <v>45064.21875</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>45064.25555555556</v>
@@ -23014,7 +23014,7 @@
         <v>45064.85069444445</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45064.62430555555</v>
+        <v>45064.625</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>45064.68263888889</v>
@@ -23111,7 +23111,7 @@
         <v>45150.20833333334</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45149.76875</v>
+        <v>45149.77430555555</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>45150.05694444444</v>
@@ -23303,7 +23303,7 @@
         <v>45156.02986111111</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45155.10277777778</v>
+        <v>45155.10763888889</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>45155.4625</v>
@@ -23400,7 +23400,7 @@
         <v>45156.36875</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45156.03055555555</v>
+        <v>45156.03263888889</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>45156.16319444445</v>
@@ -23497,7 +23497,7 @@
         <v>45234.29166666666</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45233.94722222222</v>
+        <v>45233.95069444444</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>45234.13611111111</v>
@@ -23594,7 +23594,7 @@
         <v>45234.44652777778</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45234.30347222222</v>
+        <v>45234.30416666667</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>45234.33888888889</v>
@@ -23786,7 +23786,7 @@
         <v>45313.3375</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45312.96597222222</v>
+        <v>45312.96805555555</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>45313.11111111111</v>
@@ -23974,7 +23974,7 @@
         <v>45643.37916666667</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45643.02430555555</v>
+        <v>45643.02986111111</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>45643.29305555556</v>
@@ -24156,7 +24156,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43940.2125</v>
+        <v>43940.21597222222</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>43940.57638888889</v>
@@ -24280,7 +24280,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>44037.96597222222</v>
+        <v>44037.97222222222</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>44038.39513888889</v>
@@ -24342,7 +24342,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>44064.80347222222</v>
+        <v>44064.81388888889</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>44065.475</v>
@@ -24404,7 +24404,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>44147.97708333333</v>
+        <v>44147.98611111111</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>44148.47222222222</v>
@@ -24466,7 +24466,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>44184.86041666667</v>
+        <v>44184.87222222222</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>44185.57916666667</v>
@@ -24714,7 +24714,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>44301.84791666667</v>
+        <v>44301.85972222222</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>44302.62361111111</v>
@@ -24896,7 +24896,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>44326.26666666667</v>
+        <v>44326.27361111111</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>44326.76388888889</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>251453</v>
+        <v>244378</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>44377.95347222222</v>
+        <v>44377.96388888889</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>44378.60416666666</v>
@@ -25248,7 +25248,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>44430.32569444444</v>
+        <v>44430.33055555556</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>44430.68333333333</v>
@@ -25276,7 +25276,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>129081</v>
+        <v>125525</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>44436.55763888889</v>
+        <v>44436.56111111111</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>44436.77777777778</v>
@@ -25392,7 +25392,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>49141</v>
+        <v>47586</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>44437.08055555556</v>
+        <v>44437.08194444444</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>44437.27569444444</v>
@@ -25450,7 +25450,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>38503</v>
+        <v>37950</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>44464.76805555556</v>
+        <v>44464.77708333333</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>44465.35486111111</v>
@@ -25508,7 +25508,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>30774</v>
+        <v>28824</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>44473.02152777778</v>
+        <v>44473.02708333333</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>44473.34166666667</v>
@@ -25596,7 +25596,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>44474.07638888889</v>
+        <v>44474.07916666667</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>44474.26319444444</v>
@@ -25624,7 +25624,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>35245</v>
+        <v>34191</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>44483.96666666667</v>
+        <v>44483.97569444445</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>44484.52291666667</v>
@@ -25682,7 +25682,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>316048</v>
+        <v>305765</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>44499.91736111111</v>
+        <v>44499.92152777778</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>44500.14166666667</v>
@@ -25740,7 +25740,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>51040</v>
+        <v>49141</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>44503.58541666667</v>
+        <v>44503.59513888889</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>44504.21180555555</v>
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>403651</v>
+        <v>391170</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>44527.95833333334</v>
+        <v>44527.96875</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>44528.63888888889</v>
@@ -25856,7 +25856,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>474401</v>
+        <v>459866</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>44557.42847222222</v>
+        <v>44557.43125</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>44557.59583333333</v>
@@ -25914,7 +25914,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>26468</v>
+        <v>25526</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>44586.54513888889</v>
+        <v>44586.54652777778</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>44586.92777777778</v>
@@ -26030,7 +26030,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>149878</v>
+        <v>148785</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>44593.51527777778</v>
+        <v>44593.51736111111</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>44593.67777777778</v>
@@ -26122,7 +26122,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>44627.93472222222</v>
+        <v>44627.94097222222</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>44628.31736111111</v>
@@ -26150,7 +26150,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>149878</v>
+        <v>144991</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>44628.61527777778</v>
+        <v>44628.62152777778</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>44628.97777777778</v>
@@ -26208,7 +26208,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>134421</v>
+        <v>129795</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>44631.82847222222</v>
+        <v>44631.83125</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>44632.01875</v>
@@ -26266,7 +26266,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>8001</v>
+        <v>7503</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>44659.57638888889</v>
+        <v>44659.58194444444</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>44660.075</v>
@@ -26310,25 +26310,25 @@
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
         <v>120</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>最近候选簇内有 7 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>255255</v>
+        <v>249571</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -26354,7 +26354,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>44668.64791666667</v>
+        <v>44668.65</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>44668.87152777778</v>
@@ -26478,7 +26478,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>44697.07986111111</v>
+        <v>44697.08333333334</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>44697.48333333333</v>
@@ -26536,7 +26536,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>44702.61875</v>
+        <v>44702.62083333333</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>44702.76944444444</v>
@@ -26550,21 +26550,21 @@
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>120</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>最近候选簇内有 3 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>22791</v>
+        <v>22155</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>44721.01944444444</v>
+        <v>44721.02013888889</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>44721.08333333334</v>
@@ -26684,7 +26684,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3916</v>
+        <v>3828</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>44729.02916666667</v>
+        <v>44729.04236111111</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>44729.82361111111</v>
@@ -26728,25 +26728,25 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
         <v>120</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>检测到 2 个相互间隔超过 120 分钟的候选簇；仅保留距离 ICME 本体前端最近的候选簇，其余较远候选簇已舍弃。</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>648635</v>
+        <v>627146</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -26772,7 +26772,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>44734.12777777778</v>
+        <v>44734.12847222222</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>44734.26458333333</v>
@@ -26800,7 +26800,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>18721</v>
+        <v>18528</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>44740.34027777778</v>
+        <v>44740.34375</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>44740.57013888889</v>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>51253</v>
+        <v>49628</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>44745.25069444445</v>
+        <v>44745.25833333333</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>44745.67152777778</v>
@@ -26974,7 +26974,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>179128</v>
+        <v>172561</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>44767.26666666667</v>
+        <v>44767.27152777778</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>44767.61180555556</v>
@@ -27076,21 +27076,21 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
         <v>4</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3</v>
       </c>
       <c r="L51" t="n">
         <v>120</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>最近候选簇内有 4 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 5 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>119396</v>
+        <v>115966</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>44804.90625</v>
+        <v>44804.9125</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>44805.3125</v>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>167910</v>
+        <v>163878</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>44810.41736111111</v>
+        <v>44810.43472222222</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>44811.46041666667</v>
@@ -27206,7 +27206,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1121016</v>
+        <v>1083866</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>44812.87638888889</v>
+        <v>44812.87847222222</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>44813.01805555556</v>
@@ -27264,7 +27264,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>20100</v>
+        <v>19503</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>44817.71597222222</v>
+        <v>44817.71944444445</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>44817.93055555555</v>
@@ -27322,7 +27322,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>46665</v>
+        <v>45150</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>44921.22291666667</v>
+        <v>44921.22638888889</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>44921.47708333333</v>
@@ -27762,7 +27762,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>44964.53194444445</v>
+        <v>44964.53958333333</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>44965.25625</v>
@@ -27820,7 +27820,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>44974.58541666667</v>
+        <v>44974.59375</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>44975.02361111111</v>
@@ -27848,7 +27848,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>196878</v>
+        <v>189420</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>44976.41527777778</v>
+        <v>44976.42152777778</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>44976.8</v>
@@ -27906,7 +27906,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>148410</v>
+        <v>143496</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>1</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>44999.04722222222</v>
+        <v>44999.04861111111</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>44999.15625</v>
@@ -28110,7 +28110,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45006.51597222222</v>
+        <v>45006.51736111111</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>45006.61180555556</v>
@@ -28138,7 +28138,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>9045</v>
+        <v>8778</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45026.19027777778</v>
+        <v>45026.19513888889</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>45026.45</v>
@@ -28196,7 +28196,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>68635</v>
+        <v>66066</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45038.33472222222</v>
+        <v>45038.33611111111</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>45038.40277777778</v>
@@ -28254,7 +28254,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>4465</v>
+        <v>4278</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45048.91944444444</v>
+        <v>45048.92083333333</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>45049.06736111111</v>
@@ -28312,7 +28312,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>21945</v>
+        <v>21528</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45049.43333333333</v>
+        <v>45049.43402777778</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>45049.48611111111</v>
@@ -28370,7 +28370,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2628</v>
+        <v>2556</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45064.21805555555</v>
+        <v>45064.21875</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>45064.25555555556</v>
@@ -28462,7 +28462,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45064.62430555555</v>
+        <v>45064.625</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>45064.68263888889</v>
@@ -28524,7 +28524,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45075.02708333333</v>
+        <v>45075.03402777778</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>45075.38194444445</v>
@@ -28582,7 +28582,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45103.01111111111</v>
+        <v>45103.03055555555</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>45104.15</v>
@@ -28640,7 +28640,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45104.84513888889</v>
+        <v>45104.84791666667</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>45105.03472222222</v>
@@ -28668,7 +28668,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>36315</v>
+        <v>35245</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45120.73125</v>
+        <v>45120.73194444444</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>45120.80625</v>
@@ -28726,7 +28726,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>5460</v>
+        <v>5356</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45125.25625</v>
+        <v>45125.25694444445</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>45125.32013888889</v>
@@ -28784,7 +28784,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3916</v>
+        <v>3828</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45125.71319444444</v>
+        <v>45125.71458333333</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>45125.84166666667</v>
@@ -28842,7 +28842,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>16471</v>
+        <v>16110</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45131.50555555556</v>
+        <v>45131.50625</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>45131.58194444444</v>
@@ -28958,7 +28958,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>5666</v>
+        <v>5565</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45133.91666666666</v>
+        <v>45133.91944444444</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>45134.06805555556</v>
@@ -29016,7 +29016,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>23005</v>
+        <v>22155</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45149.76875</v>
+        <v>45149.77430555555</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>45150.05694444444</v>
@@ -29170,7 +29170,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45155.10277777778</v>
+        <v>45155.10763888889</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>45155.4625</v>
@@ -29232,7 +29232,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45156.03055555555</v>
+        <v>45156.03263888889</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>45156.16319444445</v>
@@ -29352,7 +29352,7 @@
         <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45175.84930555556</v>
+        <v>45175.85833333333</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>45176.37361111111</v>
@@ -29366,25 +29366,25 @@
         <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L90" t="n">
         <v>120</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
+          <t>最近候选簇内有 10 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>278421</v>
+        <v>268772</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -29410,7 +29410,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45177.81388888889</v>
+        <v>45177.81527777778</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>45177.95416666667</v>
@@ -29424,25 +29424,25 @@
         <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>120</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>该 ICME 仅检出 1 个候选区，直接保留。</t>
+          <t>最近候选簇内有 2 个候选区，但合并后的整体区间未通过判据；为避免输出不符合物理阈值的长区间，保留其中距离 ICME 本体前端最近的原始有效区。</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>19701</v>
+        <v>19306</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>弱典型密度堆积区</t>
+          <t>非典型密度堆积区</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -29468,7 +29468,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45178.44513888889</v>
+        <v>45178.45208333333</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>45178.83333333334</v>
@@ -29496,7 +29496,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>151175</v>
+        <v>145671</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45188.1</v>
+        <v>45188.10347222222</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>45188.30625</v>
@@ -29554,7 +29554,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>43036</v>
+        <v>41581</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45189.03263888889</v>
+        <v>45189.03680555556</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>45189.29097222222</v>
@@ -29612,7 +29612,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>67861</v>
+        <v>65668</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45209.93888888889</v>
+        <v>45209.94305555556</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>45210.19236111111</v>
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>65306</v>
+        <v>63155</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45216.43333333333</v>
+        <v>45216.43958333333</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>45216.89027777778</v>
@@ -29728,7 +29728,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>211035</v>
+        <v>205185</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45227.25416666667</v>
+        <v>45227.26111111111</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>45227.64652777778</v>
@@ -29786,7 +29786,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>154526</v>
+        <v>148961</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45233.94722222222</v>
+        <v>45233.95069444444</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>45234.13611111111</v>
@@ -29878,7 +29878,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45234.30347222222</v>
+        <v>45234.30416666667</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>45234.33888888889</v>
@@ -30002,7 +30002,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45241.38472222222</v>
+        <v>45241.40069444444</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>45242.30069444444</v>
@@ -30030,7 +30030,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>862050</v>
+        <v>832058</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45260.44930555556</v>
+        <v>45260.45555555556</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>45260.78680555556</v>
@@ -30088,7 +30088,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>113288</v>
+        <v>109007</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>1</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45261.10208333333</v>
+        <v>45261.10277777778</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>45261.19305555556</v>
@@ -30146,7 +30146,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>8128</v>
+        <v>8001</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45270.88541666666</v>
+        <v>45270.89444444444</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>45271.38888888889</v>
@@ -30204,7 +30204,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2257</v>
+        <v>1737</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>1</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45289.10277777778</v>
+        <v>45289.11041666667</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>45289.50625</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>166433</v>
+        <v>160141</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>1</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45312.96597222222</v>
+        <v>45312.96805555555</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>45313.11111111111</v>
@@ -30470,7 +30470,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45369.70555555556</v>
+        <v>45369.71111111111</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>45370.05763888889</v>
@@ -30498,7 +30498,7 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>8550</v>
+        <v>7102</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45374.56388888889</v>
+        <v>45374.56527777778</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>45374.72083333333</v>
@@ -30556,7 +30556,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>24753</v>
+        <v>24310</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45402.04166666666</v>
+        <v>45402.04791666667</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>45402.47361111111</v>
@@ -30614,7 +30614,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>107764</v>
+        <v>103300</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>1</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45421.66597222222</v>
+        <v>45421.66805555556</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>45421.79722222222</v>
@@ -30672,7 +30672,7 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>17205</v>
+        <v>16653</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45433.33958333333</v>
+        <v>45433.34861111111</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>45433.90694444445</v>
@@ -30730,7 +30730,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>327776</v>
+        <v>317285</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>1</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45457.00347222222</v>
+        <v>45457.00416666667</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>45457.07083333333</v>
@@ -30788,7 +30788,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>4371</v>
+        <v>4278</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45497.725</v>
+        <v>45497.73055555556</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>45498.08333333334</v>
@@ -30904,7 +30904,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>131328</v>
+        <v>127260</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>1</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45499.86041666667</v>
+        <v>45499.86597222222</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>45500.19305555556</v>
@@ -30962,7 +30962,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>113050</v>
+        <v>109278</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45501.98055555556</v>
+        <v>45501.98263888889</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>45502.11041666667</v>
@@ -31078,7 +31078,7 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>16836</v>
+        <v>16290</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45515.42291666667</v>
+        <v>45515.425</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>45515.53055555555</v>
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>9122</v>
+        <v>8672</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>1</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45530.34305555555</v>
+        <v>45530.34930555556</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>45530.76527777778</v>
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>179595</v>
+        <v>174195</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>1</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45539.58125</v>
+        <v>45539.58333333334</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>45539.69513888889</v>
@@ -31310,7 +31310,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>12880</v>
+        <v>12403</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>1</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45540.82569444444</v>
+        <v>45540.82638888889</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>45540.87083333333</v>
@@ -31426,7 +31426,7 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1891</v>
+        <v>1830</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>1</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45540.94791666666</v>
+        <v>45540.94861111111</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>45540.96388888889</v>
@@ -31484,7 +31484,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>1</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45540.99652777778</v>
+        <v>45540.99722222222</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>45541.01736111111</v>
@@ -31542,7 +31542,7 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>1</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45541.05555555555</v>
+        <v>45541.05833333333</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>45541.31875</v>
@@ -31600,7 +31600,7 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>70500</v>
+        <v>69006</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>1</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45542.47291666667</v>
+        <v>45542.47708333333</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>45542.74236111111</v>
@@ -31658,7 +31658,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>71306</v>
+        <v>69236</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>1</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45545.16319444445</v>
+        <v>45545.16666666666</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>45545.34652777778</v>
@@ -31716,7 +31716,7 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>33930</v>
+        <v>32640</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45546.63194444445</v>
+        <v>45546.63402777778</v>
       </c>
       <c r="G131" s="2" t="n">
         <v>45546.83888888889</v>
@@ -31774,7 +31774,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>43365</v>
+        <v>42486</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>1</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45565.85833333333</v>
+        <v>45565.86041666667</v>
       </c>
       <c r="G132" s="2" t="n">
         <v>45565.98541666667</v>
@@ -31832,7 +31832,7 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>16110</v>
+        <v>15576</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>1</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45569.18055555555</v>
+        <v>45569.18194444444</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>45569.23888888889</v>
@@ -31890,7 +31890,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>3240</v>
+        <v>3081</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>1</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45574.63055555556</v>
+        <v>45574.63194444445</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>45574.67777777778</v>
@@ -31948,7 +31948,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>2080</v>
+        <v>1953</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>1</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45577.93888888889</v>
+        <v>45577.94027777778</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>45578.0125</v>
@@ -32006,7 +32006,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>5253</v>
+        <v>5050</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>1</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45578.08680555555</v>
+        <v>45578.08888888889</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>45578.19652777778</v>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>11935</v>
+        <v>11476</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>1</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45578.71944444445</v>
+        <v>45578.72222222222</v>
       </c>
       <c r="G138" s="2" t="n">
         <v>45578.90902777778</v>
@@ -32180,7 +32180,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>36315</v>
+        <v>35245</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>1</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45603.15416666667</v>
+        <v>45603.15625</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>45603.27638888889</v>
@@ -32238,7 +32238,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>14878</v>
+        <v>14365</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>1</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45608.17708333334</v>
+        <v>45608.17777777778</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>45608.25763888889</v>
@@ -32470,7 +32470,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>6328</v>
+        <v>6216</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>1</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45643.02430555555</v>
+        <v>45643.02986111111</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>45643.29305555556</v>
@@ -32620,7 +32620,7 @@
         <v>1</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45657.75416666667</v>
+        <v>45657.75833333333</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>45658.00486111111</v>
@@ -32648,7 +32648,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>63903</v>
+        <v>61776</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>1</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>45658.24305555555</v>
+        <v>45658.24375</v>
       </c>
       <c r="G147" s="2" t="n">
         <v>45658.29166666666</v>
@@ -32706,7 +32706,7 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>2211</v>
+        <v>2145</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>1</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45684.28680555556</v>
+        <v>45684.2875</v>
       </c>
       <c r="G151" s="2" t="n">
         <v>45684.34583333333</v>
@@ -32938,7 +32938,7 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>3321</v>
+        <v>3240</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>1</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>45689.75347222222</v>
+        <v>45689.75902777778</v>
       </c>
       <c r="G152" s="2" t="n">
         <v>45690.24027777778</v>
@@ -32996,7 +32996,7 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>243253</v>
+        <v>237705</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>1</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45708.54652777778</v>
+        <v>45708.54722222222</v>
       </c>
       <c r="G153" s="2" t="n">
         <v>45708.64097222222</v>
@@ -33054,7 +33054,7 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>8778</v>
+        <v>8646</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>1</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45709.89583333334</v>
+        <v>45709.89722222222</v>
       </c>
       <c r="G154" s="2" t="n">
         <v>45709.97013888889</v>
@@ -33112,7 +33112,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>5356</v>
+        <v>5151</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>1</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45710.28958333333</v>
+        <v>45710.29166666666</v>
       </c>
       <c r="G155" s="2" t="n">
         <v>45710.45069444444</v>
@@ -33170,7 +33170,7 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>26106</v>
+        <v>25425</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>1</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45711.21805555555</v>
+        <v>45711.225</v>
       </c>
       <c r="G156" s="2" t="n">
         <v>45711.65763888889</v>
@@ -33214,10 +33214,10 @@
         <v>1</v>
       </c>
       <c r="J156" t="n">
+        <v>6</v>
+      </c>
+      <c r="K156" t="n">
         <v>5</v>
-      </c>
-      <c r="K156" t="n">
-        <v>4</v>
       </c>
       <c r="L156" t="n">
         <v>120</v>
@@ -33228,7 +33228,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>195020</v>
+        <v>188775</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>1</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>45719.56388888889</v>
+        <v>45719.56875</v>
       </c>
       <c r="G157" s="2" t="n">
         <v>45719.84375</v>
@@ -33286,7 +33286,7 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>79800</v>
+        <v>77028</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>1</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>45770.98125</v>
+        <v>45770.98541666667</v>
       </c>
       <c r="G158" s="2" t="n">
         <v>45771.28402777778</v>
@@ -33344,7 +33344,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>36424</v>
+        <v>36397</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
